--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,6 +1188,5826 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128452297</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>586593</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7090373</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128454303</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>586789</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7090238</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128456150</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>587092</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7090041</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128453289</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>586738</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7090296</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128456020</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>587087</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7090081</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128456801</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91519</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>586808</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7090047</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128456148</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>587092</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7090041</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128454030</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>586773</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7090298</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128453887</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>586767</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7090284</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128456677</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>586919</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7090073</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128455756</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92676</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>587055</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7090173</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128454707</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>586897</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7090212</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128453418</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>586731</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7090285</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128452869</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>586682</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7090334</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128453928</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>586768</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7090309</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128454471</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>586884</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7090162</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128454384</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>586835</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7090189</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128456660</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80163</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>586916</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7090085</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128456875</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>586751</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7090092</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128455293</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>587050</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7090143</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128452844</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>586675</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7090334</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128452701</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>586641</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7090355</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128455272</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>587051</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7090142</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128454846</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>586924</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7090205</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128455546</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>587028</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7090170</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128452918</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>586693</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7090373</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128454639</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>353</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>586863</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7090231</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128455740</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>587055</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7090173</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128456386</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92660</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>586982</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7090061</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128456612</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>586932</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7090054</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128456454</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>586965</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7090059</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128455537</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>587026</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7090169</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128453864</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>586776</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7090285</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128452657</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78010</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>586636</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7090354</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128454684</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>586912</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7090206</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128454512</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>586853</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7090161</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128456473</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>586959</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7090058</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128455049</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>586957</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7090160</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128457243</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>353</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>586620</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7090201</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128454373</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>586837</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7090202</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128454343</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>586829</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7090210</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128454991</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91519</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>586930</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7090184</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128456368</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91323</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>586986</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7090055</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128456539</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>586940</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7090064</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128453832</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>586762</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7090294</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128453795</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>586761</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7090287</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128452749</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>353</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>586640</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7090343</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128456430</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92676</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>586964</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7090058</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128455401</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>353</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>587046</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7090160</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128455058</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>586958</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7090158</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128452666</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>586636</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7090355</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128454284</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>586798</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7090261</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128455902</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>587083</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7090163</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128455876</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>353</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>587083</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7090165</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128455941</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>587080</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7090141</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128457035</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>586687</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7090150</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128453037</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>586731</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7090327</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128452593</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>586637</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7090363</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128453255</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78699</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>353</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>586727</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7090310</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128456064</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>587101</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7090077</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1191,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128452297</v>
+        <v>128454303</v>
       </c>
       <c r="B6" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,21 +1202,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586593</v>
+        <v>586789</v>
       </c>
       <c r="R6" t="n">
-        <v>7090373</v>
+        <v>7090238</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128454303</v>
+        <v>128456150</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586789</v>
+        <v>587092</v>
       </c>
       <c r="R7" t="n">
-        <v>7090238</v>
+        <v>7090041</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128456150</v>
+        <v>128452297</v>
       </c>
       <c r="B8" t="n">
-        <v>78790</v>
+        <v>79650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,21 +1396,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587092</v>
+        <v>586593</v>
       </c>
       <c r="R8" t="n">
-        <v>7090041</v>
+        <v>7090373</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128453289</v>
+        <v>128456020</v>
       </c>
       <c r="B9" t="n">
-        <v>91378</v>
+        <v>92650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586738</v>
+        <v>587087</v>
       </c>
       <c r="R9" t="n">
-        <v>7090296</v>
+        <v>7090081</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456020</v>
+        <v>128453289</v>
       </c>
       <c r="B10" t="n">
-        <v>92648</v>
+        <v>91380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587087</v>
+        <v>586738</v>
       </c>
       <c r="R10" t="n">
-        <v>7090081</v>
+        <v>7090296</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1679,7 +1679,7 @@
         <v>128456801</v>
       </c>
       <c r="B11" t="n">
-        <v>91519</v>
+        <v>91521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128456148</v>
+        <v>128454030</v>
       </c>
       <c r="B12" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587092</v>
+        <v>586773</v>
       </c>
       <c r="R12" t="n">
-        <v>7090041</v>
+        <v>7090298</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128454030</v>
+        <v>128456148</v>
       </c>
       <c r="B13" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586773</v>
+        <v>587092</v>
       </c>
       <c r="R13" t="n">
-        <v>7090298</v>
+        <v>7090041</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128453887</v>
+        <v>128456677</v>
       </c>
       <c r="B14" t="n">
-        <v>79650</v>
+        <v>78699</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586767</v>
+        <v>586919</v>
       </c>
       <c r="R14" t="n">
-        <v>7090284</v>
+        <v>7090073</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128456677</v>
+        <v>128453887</v>
       </c>
       <c r="B15" t="n">
-        <v>78699</v>
+        <v>79650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586919</v>
+        <v>586767</v>
       </c>
       <c r="R15" t="n">
-        <v>7090073</v>
+        <v>7090284</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2164,7 +2164,7 @@
         <v>128455756</v>
       </c>
       <c r="B16" t="n">
-        <v>92676</v>
+        <v>92678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>128454707</v>
       </c>
       <c r="B17" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>128453418</v>
       </c>
       <c r="B18" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,32 +2549,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128453928</v>
+        <v>128454384</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>92650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586768</v>
+        <v>586835</v>
       </c>
       <c r="R20" t="n">
-        <v>7090309</v>
+        <v>7090189</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2646,32 +2646,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128454471</v>
+        <v>128456660</v>
       </c>
       <c r="B21" t="n">
-        <v>78790</v>
+        <v>80163</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586884</v>
+        <v>586916</v>
       </c>
       <c r="R21" t="n">
-        <v>7090162</v>
+        <v>7090085</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,32 +2743,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128454384</v>
+        <v>128454471</v>
       </c>
       <c r="B22" t="n">
-        <v>92648</v>
+        <v>78790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586835</v>
+        <v>586884</v>
       </c>
       <c r="R22" t="n">
-        <v>7090189</v>
+        <v>7090162</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,32 +2840,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128456660</v>
+        <v>128453928</v>
       </c>
       <c r="B23" t="n">
-        <v>80163</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586916</v>
+        <v>586768</v>
       </c>
       <c r="R23" t="n">
-        <v>7090085</v>
+        <v>7090309</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2937,32 +2937,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128456875</v>
+        <v>128452701</v>
       </c>
       <c r="B24" t="n">
-        <v>78790</v>
+        <v>92650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586751</v>
+        <v>586641</v>
       </c>
       <c r="R24" t="n">
-        <v>7090092</v>
+        <v>7090355</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128452701</v>
+        <v>128456875</v>
       </c>
       <c r="B27" t="n">
-        <v>92648</v>
+        <v>78790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586641</v>
+        <v>586751</v>
       </c>
       <c r="R27" t="n">
-        <v>7090355</v>
+        <v>7090092</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3328,7 +3328,7 @@
         <v>128455272</v>
       </c>
       <c r="B28" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3616,32 +3616,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128452918</v>
+        <v>128456612</v>
       </c>
       <c r="B31" t="n">
-        <v>92648</v>
+        <v>79650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586693</v>
+        <v>586932</v>
       </c>
       <c r="R31" t="n">
-        <v>7090373</v>
+        <v>7090054</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128454639</v>
+        <v>128456454</v>
       </c>
       <c r="B32" t="n">
-        <v>78699</v>
+        <v>79650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3724,21 +3724,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586863</v>
+        <v>586965</v>
       </c>
       <c r="R32" t="n">
-        <v>7090231</v>
+        <v>7090059</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128455740</v>
+        <v>128454639</v>
       </c>
       <c r="B33" t="n">
-        <v>92652</v>
+        <v>78699</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587055</v>
+        <v>586863</v>
       </c>
       <c r="R33" t="n">
-        <v>7090173</v>
+        <v>7090231</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3910,7 +3910,7 @@
         <v>128456386</v>
       </c>
       <c r="B34" t="n">
-        <v>92660</v>
+        <v>92662</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4004,32 +4004,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128456612</v>
+        <v>128452918</v>
       </c>
       <c r="B35" t="n">
-        <v>79650</v>
+        <v>92650</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586932</v>
+        <v>586693</v>
       </c>
       <c r="R35" t="n">
-        <v>7090054</v>
+        <v>7090373</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128456454</v>
+        <v>128455740</v>
       </c>
       <c r="B36" t="n">
-        <v>79650</v>
+        <v>92654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586965</v>
+        <v>587055</v>
       </c>
       <c r="R36" t="n">
-        <v>7090059</v>
+        <v>7090173</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128455537</v>
+        <v>128453864</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>92654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587026</v>
+        <v>586776</v>
       </c>
       <c r="R37" t="n">
-        <v>7090169</v>
+        <v>7090285</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4295,32 +4295,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128453864</v>
+        <v>128454684</v>
       </c>
       <c r="B38" t="n">
-        <v>92652</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586776</v>
+        <v>586912</v>
       </c>
       <c r="R38" t="n">
-        <v>7090285</v>
+        <v>7090206</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128452657</v>
+        <v>128454512</v>
       </c>
       <c r="B39" t="n">
-        <v>78010</v>
+        <v>79032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4403,21 +4403,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586636</v>
+        <v>586853</v>
       </c>
       <c r="R39" t="n">
-        <v>7090354</v>
+        <v>7090161</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128454684</v>
+        <v>128452657</v>
       </c>
       <c r="B40" t="n">
-        <v>79032</v>
+        <v>78010</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586912</v>
+        <v>586636</v>
       </c>
       <c r="R40" t="n">
-        <v>7090206</v>
+        <v>7090354</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4586,7 +4586,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128454512</v>
+        <v>128455537</v>
       </c>
       <c r="B41" t="n">
         <v>79032</v>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586853</v>
+        <v>587026</v>
       </c>
       <c r="R41" t="n">
-        <v>7090161</v>
+        <v>7090169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4686,7 +4686,7 @@
         <v>128456473</v>
       </c>
       <c r="B42" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128455049</v>
+        <v>128457243</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586957</v>
+        <v>586620</v>
       </c>
       <c r="R43" t="n">
-        <v>7090160</v>
+        <v>7090201</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128457243</v>
+        <v>128454373</v>
       </c>
       <c r="B44" t="n">
-        <v>78699</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4888,21 +4888,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586620</v>
+        <v>586837</v>
       </c>
       <c r="R44" t="n">
-        <v>7090201</v>
+        <v>7090202</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128454373</v>
+        <v>128454343</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586837</v>
+        <v>586829</v>
       </c>
       <c r="R45" t="n">
-        <v>7090202</v>
+        <v>7090210</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128454343</v>
+        <v>128455049</v>
       </c>
       <c r="B46" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5082,21 +5082,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586829</v>
+        <v>586957</v>
       </c>
       <c r="R46" t="n">
-        <v>7090210</v>
+        <v>7090160</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5171,7 +5171,7 @@
         <v>128454991</v>
       </c>
       <c r="B47" t="n">
-        <v>91519</v>
+        <v>91521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>128456368</v>
       </c>
       <c r="B48" t="n">
-        <v>91323</v>
+        <v>91325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>128456539</v>
       </c>
       <c r="B49" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5459,32 +5459,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128453832</v>
+        <v>128452749</v>
       </c>
       <c r="B50" t="n">
-        <v>92648</v>
+        <v>78699</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586762</v>
+        <v>586640</v>
       </c>
       <c r="R50" t="n">
-        <v>7090294</v>
+        <v>7090343</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5556,32 +5556,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128453795</v>
+        <v>128453832</v>
       </c>
       <c r="B51" t="n">
-        <v>78790</v>
+        <v>92650</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586761</v>
+        <v>586762</v>
       </c>
       <c r="R51" t="n">
-        <v>7090287</v>
+        <v>7090294</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128452749</v>
+        <v>128453795</v>
       </c>
       <c r="B52" t="n">
-        <v>78699</v>
+        <v>78790</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5664,21 +5664,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586640</v>
+        <v>586761</v>
       </c>
       <c r="R52" t="n">
-        <v>7090343</v>
+        <v>7090287</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5750,10 +5750,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128456430</v>
+        <v>128455401</v>
       </c>
       <c r="B53" t="n">
-        <v>92676</v>
+        <v>78699</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5761,21 +5761,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586964</v>
+        <v>587046</v>
       </c>
       <c r="R53" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128455401</v>
+        <v>128456430</v>
       </c>
       <c r="B54" t="n">
-        <v>78699</v>
+        <v>92678</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5858,21 +5858,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>587046</v>
+        <v>586964</v>
       </c>
       <c r="R54" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5944,10 +5944,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455058</v>
+        <v>128455902</v>
       </c>
       <c r="B55" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586958</v>
+        <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090158</v>
+        <v>7090163</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6041,10 +6041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128452666</v>
+        <v>128455876</v>
       </c>
       <c r="B56" t="n">
-        <v>78790</v>
+        <v>78699</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6052,21 +6052,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586636</v>
+        <v>587083</v>
       </c>
       <c r="R56" t="n">
-        <v>7090355</v>
+        <v>7090165</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128454284</v>
+        <v>128455941</v>
       </c>
       <c r="B57" t="n">
-        <v>78790</v>
+        <v>92644</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586798</v>
+        <v>587080</v>
       </c>
       <c r="R57" t="n">
-        <v>7090261</v>
+        <v>7090141</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6235,10 +6235,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128455902</v>
+        <v>128455058</v>
       </c>
       <c r="B58" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>587083</v>
+        <v>586958</v>
       </c>
       <c r="R58" t="n">
-        <v>7090163</v>
+        <v>7090158</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6332,32 +6332,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455876</v>
+        <v>128457035</v>
       </c>
       <c r="B59" t="n">
-        <v>78699</v>
+        <v>92650</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587083</v>
+        <v>586687</v>
       </c>
       <c r="R59" t="n">
-        <v>7090165</v>
+        <v>7090150</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128455941</v>
+        <v>128454284</v>
       </c>
       <c r="B60" t="n">
-        <v>92642</v>
+        <v>78790</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>587080</v>
+        <v>586798</v>
       </c>
       <c r="R60" t="n">
-        <v>7090141</v>
+        <v>7090261</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6526,32 +6526,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128457035</v>
+        <v>128452666</v>
       </c>
       <c r="B61" t="n">
-        <v>92648</v>
+        <v>78790</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586687</v>
+        <v>586636</v>
       </c>
       <c r="R61" t="n">
-        <v>7090150</v>
+        <v>7090355</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B62" t="n">
-        <v>92648</v>
+        <v>78790</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R62" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6720,32 +6720,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B63" t="n">
-        <v>78790</v>
+        <v>92650</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R63" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B64" t="n">
-        <v>78699</v>
+        <v>79032</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R64" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B65" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R65" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>128454303</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>128456150</v>
       </c>
       <c r="B7" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128452297</v>
       </c>
       <c r="B8" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128456020</v>
+        <v>128456801</v>
       </c>
       <c r="B9" t="n">
-        <v>92650</v>
+        <v>91613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587087</v>
+        <v>586808</v>
       </c>
       <c r="R9" t="n">
-        <v>7090081</v>
+        <v>7090047</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128453289</v>
+        <v>128456020</v>
       </c>
       <c r="B10" t="n">
-        <v>91380</v>
+        <v>92742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586738</v>
+        <v>587087</v>
       </c>
       <c r="R10" t="n">
-        <v>7090296</v>
+        <v>7090081</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128456801</v>
+        <v>128453289</v>
       </c>
       <c r="B11" t="n">
-        <v>91521</v>
+        <v>91472</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586808</v>
+        <v>586738</v>
       </c>
       <c r="R11" t="n">
-        <v>7090047</v>
+        <v>7090296</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1776,7 +1776,7 @@
         <v>128454030</v>
       </c>
       <c r="B12" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>128456148</v>
       </c>
       <c r="B13" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128456677</v>
       </c>
       <c r="B14" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>128453887</v>
       </c>
       <c r="B15" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,32 +2161,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B16" t="n">
-        <v>92678</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R16" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,32 +2258,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B17" t="n">
-        <v>92650</v>
+        <v>92770</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R17" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128453418</v>
+        <v>128452869</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>80217</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586731</v>
+        <v>586682</v>
       </c>
       <c r="R18" t="n">
-        <v>7090285</v>
+        <v>7090334</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128452869</v>
+        <v>128453418</v>
       </c>
       <c r="B19" t="n">
-        <v>80164</v>
+        <v>92742</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586682</v>
+        <v>586731</v>
       </c>
       <c r="R19" t="n">
-        <v>7090334</v>
+        <v>7090285</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2552,7 +2552,7 @@
         <v>128454384</v>
       </c>
       <c r="B20" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128456660</v>
       </c>
       <c r="B21" t="n">
-        <v>80163</v>
+        <v>80216</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128454471</v>
       </c>
       <c r="B22" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128453928</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>128452701</v>
       </c>
       <c r="B24" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>128455293</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>128452844</v>
       </c>
       <c r="B26" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>128456875</v>
       </c>
       <c r="B27" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>128455272</v>
       </c>
       <c r="B28" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128454846</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>128455546</v>
       </c>
       <c r="B30" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3616,32 +3616,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128456612</v>
+        <v>128455740</v>
       </c>
       <c r="B31" t="n">
-        <v>79650</v>
+        <v>92746</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586932</v>
+        <v>587055</v>
       </c>
       <c r="R31" t="n">
-        <v>7090054</v>
+        <v>7090173</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128456454</v>
+        <v>128456612</v>
       </c>
       <c r="B32" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586965</v>
+        <v>586932</v>
       </c>
       <c r="R32" t="n">
-        <v>7090059</v>
+        <v>7090054</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128454639</v>
+        <v>128456454</v>
       </c>
       <c r="B33" t="n">
-        <v>78699</v>
+        <v>79702</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586863</v>
+        <v>586965</v>
       </c>
       <c r="R33" t="n">
-        <v>7090231</v>
+        <v>7090059</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128456386</v>
+        <v>128454639</v>
       </c>
       <c r="B34" t="n">
-        <v>92662</v>
+        <v>78749</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586982</v>
+        <v>586863</v>
       </c>
       <c r="R34" t="n">
-        <v>7090061</v>
+        <v>7090231</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4004,10 +4004,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128452918</v>
+        <v>128456386</v>
       </c>
       <c r="B35" t="n">
-        <v>92650</v>
+        <v>92754</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4015,21 +4015,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586693</v>
+        <v>586982</v>
       </c>
       <c r="R35" t="n">
-        <v>7090373</v>
+        <v>7090061</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128455740</v>
+        <v>128452918</v>
       </c>
       <c r="B36" t="n">
-        <v>92654</v>
+        <v>92742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587055</v>
+        <v>586693</v>
       </c>
       <c r="R36" t="n">
-        <v>7090173</v>
+        <v>7090373</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4201,7 +4201,7 @@
         <v>128453864</v>
       </c>
       <c r="B37" t="n">
-        <v>92654</v>
+        <v>92746</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128454684</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>128454512</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>128452657</v>
       </c>
       <c r="B40" t="n">
-        <v>78010</v>
+        <v>78055</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>128455537</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,32 +4683,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128456473</v>
+        <v>128457243</v>
       </c>
       <c r="B42" t="n">
-        <v>92650</v>
+        <v>78749</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586959</v>
+        <v>586620</v>
       </c>
       <c r="R42" t="n">
-        <v>7090058</v>
+        <v>7090201</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4780,32 +4780,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128457243</v>
+        <v>128456473</v>
       </c>
       <c r="B43" t="n">
-        <v>78699</v>
+        <v>92742</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586620</v>
+        <v>586959</v>
       </c>
       <c r="R43" t="n">
-        <v>7090201</v>
+        <v>7090058</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4880,7 +4880,7 @@
         <v>128454373</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>128454343</v>
       </c>
       <c r="B45" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>128455049</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128454991</v>
       </c>
       <c r="B47" t="n">
-        <v>91521</v>
+        <v>91613</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456368</v>
+        <v>128456539</v>
       </c>
       <c r="B48" t="n">
-        <v>91325</v>
+        <v>92742</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,21 +5276,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586986</v>
+        <v>586940</v>
       </c>
       <c r="R48" t="n">
-        <v>7090055</v>
+        <v>7090064</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128456539</v>
+        <v>128456368</v>
       </c>
       <c r="B49" t="n">
-        <v>92650</v>
+        <v>91417</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586940</v>
+        <v>586986</v>
       </c>
       <c r="R49" t="n">
-        <v>7090064</v>
+        <v>7090055</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5462,7 +5462,7 @@
         <v>128452749</v>
       </c>
       <c r="B50" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>128453832</v>
       </c>
       <c r="B51" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>128453795</v>
       </c>
       <c r="B52" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>128455401</v>
       </c>
       <c r="B53" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>128456430</v>
       </c>
       <c r="B54" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,32 +5944,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455902</v>
+        <v>128455876</v>
       </c>
       <c r="B55" t="n">
-        <v>92650</v>
+        <v>78749</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5982,7 +5982,7 @@
         <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090163</v>
+        <v>7090165</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6041,10 +6041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128455876</v>
+        <v>128455941</v>
       </c>
       <c r="B56" t="n">
-        <v>78699</v>
+        <v>92736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6052,21 +6052,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587083</v>
+        <v>587080</v>
       </c>
       <c r="R56" t="n">
-        <v>7090165</v>
+        <v>7090141</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,32 +6138,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128455941</v>
+        <v>128455902</v>
       </c>
       <c r="B57" t="n">
-        <v>92644</v>
+        <v>92742</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587080</v>
+        <v>587083</v>
       </c>
       <c r="R57" t="n">
-        <v>7090141</v>
+        <v>7090163</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6238,7 +6238,7 @@
         <v>128455058</v>
       </c>
       <c r="B58" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128457035</v>
       </c>
       <c r="B59" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>128454284</v>
       </c>
       <c r="B60" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128452666</v>
       </c>
       <c r="B61" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>128452593</v>
       </c>
       <c r="B62" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128453037</v>
       </c>
       <c r="B63" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B64" t="n">
-        <v>79032</v>
+        <v>78749</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R64" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B65" t="n">
-        <v>78699</v>
+        <v>79083</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R65" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -2161,32 +2161,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>92770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R16" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,32 +2258,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B17" t="n">
-        <v>92770</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R17" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128452869</v>
+        <v>128453418</v>
       </c>
       <c r="B18" t="n">
-        <v>80217</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586682</v>
+        <v>586731</v>
       </c>
       <c r="R18" t="n">
-        <v>7090334</v>
+        <v>7090285</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128453418</v>
+        <v>128452869</v>
       </c>
       <c r="B19" t="n">
-        <v>92742</v>
+        <v>80217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586731</v>
+        <v>586682</v>
       </c>
       <c r="R19" t="n">
-        <v>7090285</v>
+        <v>7090334</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3616,32 +3616,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128455740</v>
+        <v>128454639</v>
       </c>
       <c r="B31" t="n">
-        <v>92746</v>
+        <v>78749</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587055</v>
+        <v>586863</v>
       </c>
       <c r="R31" t="n">
-        <v>7090173</v>
+        <v>7090231</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,32 +3713,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128456612</v>
+        <v>128456386</v>
       </c>
       <c r="B32" t="n">
-        <v>79702</v>
+        <v>92754</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586932</v>
+        <v>586982</v>
       </c>
       <c r="R32" t="n">
-        <v>7090054</v>
+        <v>7090061</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128456454</v>
+        <v>128452918</v>
       </c>
       <c r="B33" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586965</v>
+        <v>586693</v>
       </c>
       <c r="R33" t="n">
-        <v>7090059</v>
+        <v>7090373</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128454639</v>
+        <v>128455740</v>
       </c>
       <c r="B34" t="n">
-        <v>78749</v>
+        <v>92746</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586863</v>
+        <v>587055</v>
       </c>
       <c r="R34" t="n">
-        <v>7090231</v>
+        <v>7090173</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4004,32 +4004,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128456386</v>
+        <v>128456612</v>
       </c>
       <c r="B35" t="n">
-        <v>92754</v>
+        <v>79702</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586982</v>
+        <v>586932</v>
       </c>
       <c r="R35" t="n">
-        <v>7090061</v>
+        <v>7090054</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128452918</v>
+        <v>128456454</v>
       </c>
       <c r="B36" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586693</v>
+        <v>586965</v>
       </c>
       <c r="R36" t="n">
-        <v>7090373</v>
+        <v>7090059</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456539</v>
+        <v>128456368</v>
       </c>
       <c r="B48" t="n">
-        <v>92742</v>
+        <v>91417</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,21 +5276,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586940</v>
+        <v>586986</v>
       </c>
       <c r="R48" t="n">
-        <v>7090064</v>
+        <v>7090055</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128456368</v>
+        <v>128456539</v>
       </c>
       <c r="B49" t="n">
-        <v>91417</v>
+        <v>92742</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586986</v>
+        <v>586940</v>
       </c>
       <c r="R49" t="n">
-        <v>7090055</v>
+        <v>7090064</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6138,7 +6138,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128455902</v>
+        <v>128455058</v>
       </c>
       <c r="B57" t="n">
         <v>92742</v>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587083</v>
+        <v>586958</v>
       </c>
       <c r="R57" t="n">
-        <v>7090163</v>
+        <v>7090158</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128455058</v>
+        <v>128457035</v>
       </c>
       <c r="B58" t="n">
         <v>92742</v>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586958</v>
+        <v>586687</v>
       </c>
       <c r="R58" t="n">
-        <v>7090158</v>
+        <v>7090150</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6332,7 +6332,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128457035</v>
+        <v>128455902</v>
       </c>
       <c r="B59" t="n">
         <v>92742</v>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586687</v>
+        <v>587083</v>
       </c>
       <c r="R59" t="n">
-        <v>7090150</v>
+        <v>7090163</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B64" t="n">
-        <v>78749</v>
+        <v>79083</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R64" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B65" t="n">
-        <v>79083</v>
+        <v>78749</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R65" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128456801</v>
+        <v>128453289</v>
       </c>
       <c r="B9" t="n">
-        <v>91613</v>
+        <v>91472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586808</v>
+        <v>586738</v>
       </c>
       <c r="R9" t="n">
-        <v>7090047</v>
+        <v>7090296</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456020</v>
+        <v>128456801</v>
       </c>
       <c r="B10" t="n">
-        <v>92742</v>
+        <v>91613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587087</v>
+        <v>586808</v>
       </c>
       <c r="R10" t="n">
-        <v>7090081</v>
+        <v>7090047</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128453289</v>
+        <v>128456020</v>
       </c>
       <c r="B11" t="n">
-        <v>91472</v>
+        <v>92742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586738</v>
+        <v>587087</v>
       </c>
       <c r="R11" t="n">
-        <v>7090296</v>
+        <v>7090081</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -5459,32 +5459,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128452749</v>
+        <v>128453832</v>
       </c>
       <c r="B50" t="n">
-        <v>78749</v>
+        <v>92742</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586640</v>
+        <v>586762</v>
       </c>
       <c r="R50" t="n">
-        <v>7090343</v>
+        <v>7090294</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5556,32 +5556,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128453832</v>
+        <v>128452749</v>
       </c>
       <c r="B51" t="n">
-        <v>92742</v>
+        <v>78749</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586762</v>
+        <v>586640</v>
       </c>
       <c r="R51" t="n">
-        <v>7090294</v>
+        <v>7090343</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B62" t="n">
-        <v>78840</v>
+        <v>92742</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R62" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6720,32 +6720,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B63" t="n">
-        <v>92742</v>
+        <v>78840</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R63" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128456677</v>
+        <v>128453887</v>
       </c>
       <c r="B14" t="n">
-        <v>78749</v>
+        <v>79702</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586919</v>
+        <v>586767</v>
       </c>
       <c r="R14" t="n">
-        <v>7090073</v>
+        <v>7090284</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128453887</v>
+        <v>128456677</v>
       </c>
       <c r="B15" t="n">
-        <v>79702</v>
+        <v>78749</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586767</v>
+        <v>586919</v>
       </c>
       <c r="R15" t="n">
-        <v>7090284</v>
+        <v>7090073</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2937,32 +2937,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128452701</v>
+        <v>128455293</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586641</v>
+        <v>587050</v>
       </c>
       <c r="R24" t="n">
-        <v>7090355</v>
+        <v>7090143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128455293</v>
+        <v>128452844</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587050</v>
+        <v>586675</v>
       </c>
       <c r="R25" t="n">
-        <v>7090143</v>
+        <v>7090334</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128452844</v>
+        <v>128456875</v>
       </c>
       <c r="B26" t="n">
-        <v>80188</v>
+        <v>78840</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586675</v>
+        <v>586751</v>
       </c>
       <c r="R26" t="n">
-        <v>7090334</v>
+        <v>7090092</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128456875</v>
+        <v>128452701</v>
       </c>
       <c r="B27" t="n">
-        <v>78840</v>
+        <v>92742</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586751</v>
+        <v>586641</v>
       </c>
       <c r="R27" t="n">
-        <v>7090092</v>
+        <v>7090355</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4780,32 +4780,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128456473</v>
+        <v>128454373</v>
       </c>
       <c r="B43" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586959</v>
+        <v>586837</v>
       </c>
       <c r="R43" t="n">
-        <v>7090058</v>
+        <v>7090202</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128454373</v>
+        <v>128454343</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4888,21 +4888,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586837</v>
+        <v>586829</v>
       </c>
       <c r="R44" t="n">
-        <v>7090202</v>
+        <v>7090210</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128454343</v>
+        <v>128455049</v>
       </c>
       <c r="B45" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586829</v>
+        <v>586957</v>
       </c>
       <c r="R45" t="n">
-        <v>7090210</v>
+        <v>7090160</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5071,32 +5071,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128455049</v>
+        <v>128456473</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586957</v>
+        <v>586959</v>
       </c>
       <c r="R46" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5944,32 +5944,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455876</v>
+        <v>128455902</v>
       </c>
       <c r="B55" t="n">
-        <v>78749</v>
+        <v>92742</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5982,7 +5982,7 @@
         <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090165</v>
+        <v>7090163</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6041,10 +6041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128455941</v>
+        <v>128454284</v>
       </c>
       <c r="B56" t="n">
-        <v>92736</v>
+        <v>78840</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6052,21 +6052,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587080</v>
+        <v>586798</v>
       </c>
       <c r="R56" t="n">
-        <v>7090141</v>
+        <v>7090261</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,32 +6138,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128455058</v>
+        <v>128452666</v>
       </c>
       <c r="B57" t="n">
-        <v>92742</v>
+        <v>78840</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586958</v>
+        <v>586636</v>
       </c>
       <c r="R57" t="n">
-        <v>7090158</v>
+        <v>7090355</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6235,32 +6235,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128457035</v>
+        <v>128455876</v>
       </c>
       <c r="B58" t="n">
-        <v>92742</v>
+        <v>78749</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586687</v>
+        <v>587083</v>
       </c>
       <c r="R58" t="n">
-        <v>7090150</v>
+        <v>7090165</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6332,32 +6332,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455902</v>
+        <v>128455941</v>
       </c>
       <c r="B59" t="n">
-        <v>92742</v>
+        <v>92736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587083</v>
+        <v>587080</v>
       </c>
       <c r="R59" t="n">
-        <v>7090163</v>
+        <v>7090141</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6429,32 +6429,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128454284</v>
+        <v>128455058</v>
       </c>
       <c r="B60" t="n">
-        <v>78840</v>
+        <v>92742</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586798</v>
+        <v>586958</v>
       </c>
       <c r="R60" t="n">
-        <v>7090261</v>
+        <v>7090158</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6526,32 +6526,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128452666</v>
+        <v>128457035</v>
       </c>
       <c r="B61" t="n">
-        <v>78840</v>
+        <v>92742</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586636</v>
+        <v>586687</v>
       </c>
       <c r="R61" t="n">
-        <v>7090355</v>
+        <v>7090150</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>128454303</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>128456150</v>
       </c>
       <c r="B7" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128452297</v>
       </c>
       <c r="B8" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128453289</v>
+        <v>128456020</v>
       </c>
       <c r="B9" t="n">
-        <v>91472</v>
+        <v>92754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586738</v>
+        <v>587087</v>
       </c>
       <c r="R9" t="n">
-        <v>7090296</v>
+        <v>7090081</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456801</v>
+        <v>128453289</v>
       </c>
       <c r="B10" t="n">
-        <v>91613</v>
+        <v>91484</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586808</v>
+        <v>586738</v>
       </c>
       <c r="R10" t="n">
-        <v>7090047</v>
+        <v>7090296</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128456020</v>
+        <v>128456801</v>
       </c>
       <c r="B11" t="n">
-        <v>92742</v>
+        <v>91625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587087</v>
+        <v>586808</v>
       </c>
       <c r="R11" t="n">
-        <v>7090081</v>
+        <v>7090047</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1776,7 +1776,7 @@
         <v>128454030</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>128456148</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128453887</v>
+        <v>128456677</v>
       </c>
       <c r="B14" t="n">
-        <v>79702</v>
+        <v>78753</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586767</v>
+        <v>586919</v>
       </c>
       <c r="R14" t="n">
-        <v>7090284</v>
+        <v>7090073</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128456677</v>
+        <v>128453887</v>
       </c>
       <c r="B15" t="n">
-        <v>78749</v>
+        <v>79706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586919</v>
+        <v>586767</v>
       </c>
       <c r="R15" t="n">
-        <v>7090073</v>
+        <v>7090284</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2161,32 +2161,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B16" t="n">
-        <v>92770</v>
+        <v>92754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R16" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,32 +2258,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>92782</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R17" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2358,7 +2358,7 @@
         <v>128453418</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>128452869</v>
       </c>
       <c r="B19" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128454384</v>
+        <v>128456660</v>
       </c>
       <c r="B20" t="n">
-        <v>92742</v>
+        <v>80220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586835</v>
+        <v>586916</v>
       </c>
       <c r="R20" t="n">
-        <v>7090189</v>
+        <v>7090085</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2646,32 +2646,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456660</v>
+        <v>128454471</v>
       </c>
       <c r="B21" t="n">
-        <v>80216</v>
+        <v>78844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586916</v>
+        <v>586884</v>
       </c>
       <c r="R21" t="n">
-        <v>7090085</v>
+        <v>7090162</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128454471</v>
+        <v>128453928</v>
       </c>
       <c r="B22" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586884</v>
+        <v>586768</v>
       </c>
       <c r="R22" t="n">
-        <v>7090162</v>
+        <v>7090309</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,32 +2840,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128453928</v>
+        <v>128454384</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>92754</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586768</v>
+        <v>586835</v>
       </c>
       <c r="R23" t="n">
-        <v>7090309</v>
+        <v>7090189</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2937,32 +2937,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128455293</v>
+        <v>128452701</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>92754</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587050</v>
+        <v>586641</v>
       </c>
       <c r="R24" t="n">
-        <v>7090143</v>
+        <v>7090355</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128452844</v>
+        <v>128455293</v>
       </c>
       <c r="B25" t="n">
-        <v>80188</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586675</v>
+        <v>587050</v>
       </c>
       <c r="R25" t="n">
-        <v>7090334</v>
+        <v>7090143</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456875</v>
+        <v>128452844</v>
       </c>
       <c r="B26" t="n">
-        <v>78840</v>
+        <v>80192</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586751</v>
+        <v>586675</v>
       </c>
       <c r="R26" t="n">
-        <v>7090092</v>
+        <v>7090334</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128452701</v>
+        <v>128456875</v>
       </c>
       <c r="B27" t="n">
-        <v>92742</v>
+        <v>78844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586641</v>
+        <v>586751</v>
       </c>
       <c r="R27" t="n">
-        <v>7090355</v>
+        <v>7090092</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3328,7 +3328,7 @@
         <v>128455272</v>
       </c>
       <c r="B28" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128454846</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>128455546</v>
       </c>
       <c r="B30" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3616,32 +3616,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128454639</v>
+        <v>128456386</v>
       </c>
       <c r="B31" t="n">
-        <v>78749</v>
+        <v>92766</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586863</v>
+        <v>586982</v>
       </c>
       <c r="R31" t="n">
-        <v>7090231</v>
+        <v>7090061</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128456386</v>
+        <v>128452918</v>
       </c>
       <c r="B32" t="n">
         <v>92754</v>
@@ -3724,21 +3724,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586982</v>
+        <v>586693</v>
       </c>
       <c r="R32" t="n">
-        <v>7090061</v>
+        <v>7090373</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128452918</v>
+        <v>128455740</v>
       </c>
       <c r="B33" t="n">
-        <v>92742</v>
+        <v>92758</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586693</v>
+        <v>587055</v>
       </c>
       <c r="R33" t="n">
-        <v>7090373</v>
+        <v>7090173</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128455740</v>
+        <v>128456612</v>
       </c>
       <c r="B34" t="n">
-        <v>92746</v>
+        <v>79706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587055</v>
+        <v>586932</v>
       </c>
       <c r="R34" t="n">
-        <v>7090173</v>
+        <v>7090054</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4004,10 +4004,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128456612</v>
+        <v>128456454</v>
       </c>
       <c r="B35" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586932</v>
+        <v>586965</v>
       </c>
       <c r="R35" t="n">
-        <v>7090054</v>
+        <v>7090059</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128456454</v>
+        <v>128454639</v>
       </c>
       <c r="B36" t="n">
-        <v>79702</v>
+        <v>78753</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4112,21 +4112,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586965</v>
+        <v>586863</v>
       </c>
       <c r="R36" t="n">
-        <v>7090059</v>
+        <v>7090231</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4201,7 +4201,7 @@
         <v>128453864</v>
       </c>
       <c r="B37" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128454684</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>128454512</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>128452657</v>
       </c>
       <c r="B40" t="n">
-        <v>78055</v>
+        <v>78059</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>128455537</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128457243</v>
+        <v>128454373</v>
       </c>
       <c r="B42" t="n">
-        <v>78749</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4694,21 +4694,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586620</v>
+        <v>586837</v>
       </c>
       <c r="R42" t="n">
-        <v>7090201</v>
+        <v>7090202</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128454373</v>
+        <v>128454343</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586837</v>
+        <v>586829</v>
       </c>
       <c r="R43" t="n">
-        <v>7090202</v>
+        <v>7090210</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128454343</v>
+        <v>128455049</v>
       </c>
       <c r="B44" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4888,21 +4888,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586829</v>
+        <v>586957</v>
       </c>
       <c r="R44" t="n">
-        <v>7090210</v>
+        <v>7090160</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128455049</v>
+        <v>128457243</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>78753</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586957</v>
+        <v>586620</v>
       </c>
       <c r="R45" t="n">
-        <v>7090160</v>
+        <v>7090201</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5074,7 +5074,7 @@
         <v>128456473</v>
       </c>
       <c r="B46" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128454991</v>
       </c>
       <c r="B47" t="n">
-        <v>91613</v>
+        <v>91625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456368</v>
+        <v>128456539</v>
       </c>
       <c r="B48" t="n">
-        <v>91417</v>
+        <v>92754</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,21 +5276,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586986</v>
+        <v>586940</v>
       </c>
       <c r="R48" t="n">
-        <v>7090055</v>
+        <v>7090064</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128456539</v>
+        <v>128456368</v>
       </c>
       <c r="B49" t="n">
-        <v>92742</v>
+        <v>91429</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586940</v>
+        <v>586986</v>
       </c>
       <c r="R49" t="n">
-        <v>7090064</v>
+        <v>7090055</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5459,32 +5459,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128453832</v>
+        <v>128452749</v>
       </c>
       <c r="B50" t="n">
-        <v>92742</v>
+        <v>78753</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586762</v>
+        <v>586640</v>
       </c>
       <c r="R50" t="n">
-        <v>7090294</v>
+        <v>7090343</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5556,32 +5556,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128452749</v>
+        <v>128453832</v>
       </c>
       <c r="B51" t="n">
-        <v>78749</v>
+        <v>92754</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586640</v>
+        <v>586762</v>
       </c>
       <c r="R51" t="n">
-        <v>7090343</v>
+        <v>7090294</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5656,7 +5656,7 @@
         <v>128453795</v>
       </c>
       <c r="B52" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5750,10 +5750,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128455401</v>
+        <v>128456430</v>
       </c>
       <c r="B53" t="n">
-        <v>78749</v>
+        <v>92782</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5761,21 +5761,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>587046</v>
+        <v>586964</v>
       </c>
       <c r="R53" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128456430</v>
+        <v>128455401</v>
       </c>
       <c r="B54" t="n">
-        <v>92770</v>
+        <v>78753</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5858,21 +5858,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586964</v>
+        <v>587046</v>
       </c>
       <c r="R54" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5944,32 +5944,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455902</v>
+        <v>128455876</v>
       </c>
       <c r="B55" t="n">
-        <v>92742</v>
+        <v>78753</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5982,7 +5982,7 @@
         <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090163</v>
+        <v>7090165</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6041,32 +6041,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128454284</v>
+        <v>128455902</v>
       </c>
       <c r="B56" t="n">
-        <v>78840</v>
+        <v>92754</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586798</v>
+        <v>587083</v>
       </c>
       <c r="R56" t="n">
-        <v>7090261</v>
+        <v>7090163</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128452666</v>
+        <v>128455941</v>
       </c>
       <c r="B57" t="n">
-        <v>78840</v>
+        <v>92748</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586636</v>
+        <v>587080</v>
       </c>
       <c r="R57" t="n">
-        <v>7090355</v>
+        <v>7090141</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6235,32 +6235,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128455876</v>
+        <v>128455058</v>
       </c>
       <c r="B58" t="n">
-        <v>78749</v>
+        <v>92754</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>587083</v>
+        <v>586958</v>
       </c>
       <c r="R58" t="n">
-        <v>7090165</v>
+        <v>7090158</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6332,32 +6332,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455941</v>
+        <v>128457035</v>
       </c>
       <c r="B59" t="n">
-        <v>92736</v>
+        <v>92754</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587080</v>
+        <v>586687</v>
       </c>
       <c r="R59" t="n">
-        <v>7090141</v>
+        <v>7090150</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6429,32 +6429,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128455058</v>
+        <v>128454284</v>
       </c>
       <c r="B60" t="n">
-        <v>92742</v>
+        <v>78844</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586958</v>
+        <v>586798</v>
       </c>
       <c r="R60" t="n">
-        <v>7090158</v>
+        <v>7090261</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6526,32 +6526,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128457035</v>
+        <v>128452666</v>
       </c>
       <c r="B61" t="n">
-        <v>92742</v>
+        <v>78844</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586687</v>
+        <v>586636</v>
       </c>
       <c r="R61" t="n">
-        <v>7090150</v>
+        <v>7090355</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6626,7 +6626,7 @@
         <v>128453037</v>
       </c>
       <c r="B62" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>128452593</v>
       </c>
       <c r="B63" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B64" t="n">
-        <v>79083</v>
+        <v>78753</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R64" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B65" t="n">
-        <v>78749</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R65" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128456020</v>
+        <v>128453289</v>
       </c>
       <c r="B9" t="n">
-        <v>92754</v>
+        <v>91484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587087</v>
+        <v>586738</v>
       </c>
       <c r="R9" t="n">
-        <v>7090081</v>
+        <v>7090296</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128453289</v>
+        <v>128456801</v>
       </c>
       <c r="B10" t="n">
-        <v>91484</v>
+        <v>91625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586738</v>
+        <v>586808</v>
       </c>
       <c r="R10" t="n">
-        <v>7090296</v>
+        <v>7090047</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128456801</v>
+        <v>128456020</v>
       </c>
       <c r="B11" t="n">
-        <v>91625</v>
+        <v>92754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586808</v>
+        <v>587087</v>
       </c>
       <c r="R11" t="n">
-        <v>7090047</v>
+        <v>7090081</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2937,32 +2937,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128452701</v>
+        <v>128455293</v>
       </c>
       <c r="B24" t="n">
-        <v>92754</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586641</v>
+        <v>587050</v>
       </c>
       <c r="R24" t="n">
-        <v>7090355</v>
+        <v>7090143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128455293</v>
+        <v>128452844</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587050</v>
+        <v>586675</v>
       </c>
       <c r="R25" t="n">
-        <v>7090143</v>
+        <v>7090334</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128452844</v>
+        <v>128456875</v>
       </c>
       <c r="B26" t="n">
-        <v>80192</v>
+        <v>78844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586675</v>
+        <v>586751</v>
       </c>
       <c r="R26" t="n">
-        <v>7090334</v>
+        <v>7090092</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128456875</v>
+        <v>128452701</v>
       </c>
       <c r="B27" t="n">
-        <v>78844</v>
+        <v>92754</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586751</v>
+        <v>586641</v>
       </c>
       <c r="R27" t="n">
-        <v>7090092</v>
+        <v>7090355</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>128454303</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>128456150</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128452297</v>
       </c>
       <c r="B8" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128453289</v>
+        <v>128456020</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>92756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586738</v>
+        <v>587087</v>
       </c>
       <c r="R9" t="n">
-        <v>7090296</v>
+        <v>7090081</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1582,7 +1582,7 @@
         <v>128456801</v>
       </c>
       <c r="B10" t="n">
-        <v>91625</v>
+        <v>91627</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128456020</v>
+        <v>128453289</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>91486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587087</v>
+        <v>586738</v>
       </c>
       <c r="R11" t="n">
-        <v>7090081</v>
+        <v>7090296</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1776,7 +1776,7 @@
         <v>128454030</v>
       </c>
       <c r="B12" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>128456148</v>
       </c>
       <c r="B13" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128456677</v>
       </c>
       <c r="B14" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>128453887</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,32 +2161,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R16" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,32 +2258,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B17" t="n">
-        <v>92782</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R17" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2358,7 +2358,7 @@
         <v>128453418</v>
       </c>
       <c r="B18" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>128452869</v>
       </c>
       <c r="B19" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456660</v>
+        <v>128454384</v>
       </c>
       <c r="B20" t="n">
-        <v>80220</v>
+        <v>92756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586916</v>
+        <v>586835</v>
       </c>
       <c r="R20" t="n">
-        <v>7090085</v>
+        <v>7090189</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2646,32 +2646,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128454471</v>
+        <v>128456660</v>
       </c>
       <c r="B21" t="n">
-        <v>78844</v>
+        <v>80222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586884</v>
+        <v>586916</v>
       </c>
       <c r="R21" t="n">
-        <v>7090162</v>
+        <v>7090085</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128453928</v>
+        <v>128454471</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586768</v>
+        <v>586884</v>
       </c>
       <c r="R22" t="n">
-        <v>7090309</v>
+        <v>7090162</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,32 +2840,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128454384</v>
+        <v>128453928</v>
       </c>
       <c r="B23" t="n">
-        <v>92754</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586835</v>
+        <v>586768</v>
       </c>
       <c r="R23" t="n">
-        <v>7090189</v>
+        <v>7090309</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128455293</v>
+        <v>128452844</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587050</v>
+        <v>586675</v>
       </c>
       <c r="R24" t="n">
-        <v>7090143</v>
+        <v>7090334</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128452844</v>
+        <v>128456875</v>
       </c>
       <c r="B25" t="n">
-        <v>80192</v>
+        <v>78846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586675</v>
+        <v>586751</v>
       </c>
       <c r="R25" t="n">
-        <v>7090334</v>
+        <v>7090092</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456875</v>
+        <v>128455293</v>
       </c>
       <c r="B26" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586751</v>
+        <v>587050</v>
       </c>
       <c r="R26" t="n">
-        <v>7090092</v>
+        <v>7090143</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3231,7 +3231,7 @@
         <v>128452701</v>
       </c>
       <c r="B27" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>128455272</v>
       </c>
       <c r="B28" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128454846</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>128455546</v>
       </c>
       <c r="B30" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>128456386</v>
       </c>
       <c r="B31" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>128452918</v>
       </c>
       <c r="B32" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>128455740</v>
       </c>
       <c r="B33" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>128456612</v>
       </c>
       <c r="B34" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128456454</v>
       </c>
       <c r="B35" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>128454639</v>
       </c>
       <c r="B36" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128453864</v>
+        <v>128454684</v>
       </c>
       <c r="B37" t="n">
-        <v>92758</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586776</v>
+        <v>586912</v>
       </c>
       <c r="R37" t="n">
-        <v>7090285</v>
+        <v>7090206</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128454684</v>
+        <v>128454512</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586912</v>
+        <v>586853</v>
       </c>
       <c r="R38" t="n">
-        <v>7090206</v>
+        <v>7090161</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128454512</v>
+        <v>128455537</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586853</v>
+        <v>587026</v>
       </c>
       <c r="R39" t="n">
-        <v>7090161</v>
+        <v>7090169</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4489,32 +4489,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128452657</v>
+        <v>128453864</v>
       </c>
       <c r="B40" t="n">
-        <v>78059</v>
+        <v>92760</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586636</v>
+        <v>586776</v>
       </c>
       <c r="R40" t="n">
-        <v>7090354</v>
+        <v>7090285</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128455537</v>
+        <v>128452657</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>78061</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4597,21 +4597,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587026</v>
+        <v>586636</v>
       </c>
       <c r="R41" t="n">
-        <v>7090169</v>
+        <v>7090354</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4683,10 +4683,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128454373</v>
+        <v>128457243</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>78755</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4694,21 +4694,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586837</v>
+        <v>586620</v>
       </c>
       <c r="R42" t="n">
-        <v>7090202</v>
+        <v>7090201</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4780,32 +4780,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128454343</v>
+        <v>128456473</v>
       </c>
       <c r="B43" t="n">
-        <v>78844</v>
+        <v>92756</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586829</v>
+        <v>586959</v>
       </c>
       <c r="R43" t="n">
-        <v>7090210</v>
+        <v>7090058</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128455049</v>
+        <v>128454373</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586957</v>
+        <v>586837</v>
       </c>
       <c r="R44" t="n">
-        <v>7090160</v>
+        <v>7090202</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128457243</v>
+        <v>128454343</v>
       </c>
       <c r="B45" t="n">
-        <v>78753</v>
+        <v>78846</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586620</v>
+        <v>586829</v>
       </c>
       <c r="R45" t="n">
-        <v>7090201</v>
+        <v>7090210</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5071,32 +5071,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128456473</v>
+        <v>128455049</v>
       </c>
       <c r="B46" t="n">
-        <v>92754</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586959</v>
+        <v>586957</v>
       </c>
       <c r="R46" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5171,7 +5171,7 @@
         <v>128454991</v>
       </c>
       <c r="B47" t="n">
-        <v>91625</v>
+        <v>91627</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>128456539</v>
       </c>
       <c r="B48" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>128456368</v>
       </c>
       <c r="B49" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128452749</v>
+        <v>128453795</v>
       </c>
       <c r="B50" t="n">
-        <v>78753</v>
+        <v>78846</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,21 +5470,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586640</v>
+        <v>586761</v>
       </c>
       <c r="R50" t="n">
-        <v>7090343</v>
+        <v>7090287</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5556,32 +5556,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128453832</v>
+        <v>128452749</v>
       </c>
       <c r="B51" t="n">
-        <v>92754</v>
+        <v>78755</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586762</v>
+        <v>586640</v>
       </c>
       <c r="R51" t="n">
-        <v>7090294</v>
+        <v>7090343</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5653,32 +5653,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128453795</v>
+        <v>128453832</v>
       </c>
       <c r="B52" t="n">
-        <v>78844</v>
+        <v>92756</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586761</v>
+        <v>586762</v>
       </c>
       <c r="R52" t="n">
-        <v>7090287</v>
+        <v>7090294</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5750,10 +5750,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128456430</v>
+        <v>128455401</v>
       </c>
       <c r="B53" t="n">
-        <v>92782</v>
+        <v>78755</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5761,21 +5761,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586964</v>
+        <v>587046</v>
       </c>
       <c r="R53" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128455401</v>
+        <v>128456430</v>
       </c>
       <c r="B54" t="n">
-        <v>78753</v>
+        <v>92784</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5858,21 +5858,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>587046</v>
+        <v>586964</v>
       </c>
       <c r="R54" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5947,7 +5947,7 @@
         <v>128455876</v>
       </c>
       <c r="B55" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>128455902</v>
       </c>
       <c r="B56" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>128455941</v>
       </c>
       <c r="B57" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>128455058</v>
       </c>
       <c r="B58" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128457035</v>
       </c>
       <c r="B59" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>128454284</v>
       </c>
       <c r="B60" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>128452666</v>
       </c>
       <c r="B61" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B62" t="n">
-        <v>92754</v>
+        <v>78846</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R62" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6720,32 +6720,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B63" t="n">
-        <v>78844</v>
+        <v>92756</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R63" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6820,7 +6820,7 @@
         <v>128453255</v>
       </c>
       <c r="B64" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128456064</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -2161,32 +2161,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R16" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,32 +2258,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R17" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128454384</v>
+        <v>128456660</v>
       </c>
       <c r="B20" t="n">
-        <v>92756</v>
+        <v>80222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586835</v>
+        <v>586916</v>
       </c>
       <c r="R20" t="n">
-        <v>7090189</v>
+        <v>7090085</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2646,32 +2646,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456660</v>
+        <v>128454471</v>
       </c>
       <c r="B21" t="n">
-        <v>80222</v>
+        <v>78846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586916</v>
+        <v>586884</v>
       </c>
       <c r="R21" t="n">
-        <v>7090085</v>
+        <v>7090162</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128454471</v>
+        <v>128453928</v>
       </c>
       <c r="B22" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586884</v>
+        <v>586768</v>
       </c>
       <c r="R22" t="n">
-        <v>7090162</v>
+        <v>7090309</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,32 +2840,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128453928</v>
+        <v>128454384</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>92756</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586768</v>
+        <v>586835</v>
       </c>
       <c r="R23" t="n">
-        <v>7090309</v>
+        <v>7090189</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128452844</v>
+        <v>128455293</v>
       </c>
       <c r="B24" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586675</v>
+        <v>587050</v>
       </c>
       <c r="R24" t="n">
-        <v>7090334</v>
+        <v>7090143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456875</v>
+        <v>128452844</v>
       </c>
       <c r="B25" t="n">
-        <v>78846</v>
+        <v>80194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586751</v>
+        <v>586675</v>
       </c>
       <c r="R25" t="n">
-        <v>7090092</v>
+        <v>7090334</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128455293</v>
+        <v>128456875</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587050</v>
+        <v>586751</v>
       </c>
       <c r="R26" t="n">
-        <v>7090143</v>
+        <v>7090092</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128456612</v>
+        <v>128454639</v>
       </c>
       <c r="B34" t="n">
-        <v>79708</v>
+        <v>78755</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586932</v>
+        <v>586863</v>
       </c>
       <c r="R34" t="n">
-        <v>7090054</v>
+        <v>7090231</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128456454</v>
+        <v>128456612</v>
       </c>
       <c r="B35" t="n">
         <v>79708</v>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586965</v>
+        <v>586932</v>
       </c>
       <c r="R35" t="n">
-        <v>7090059</v>
+        <v>7090054</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128454639</v>
+        <v>128456454</v>
       </c>
       <c r="B36" t="n">
-        <v>78755</v>
+        <v>79708</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4112,21 +4112,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586863</v>
+        <v>586965</v>
       </c>
       <c r="R36" t="n">
-        <v>7090231</v>
+        <v>7090059</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4489,32 +4489,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128453864</v>
+        <v>128452657</v>
       </c>
       <c r="B40" t="n">
-        <v>92760</v>
+        <v>78061</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586776</v>
+        <v>586636</v>
       </c>
       <c r="R40" t="n">
-        <v>7090285</v>
+        <v>7090354</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4586,32 +4586,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128452657</v>
+        <v>128453864</v>
       </c>
       <c r="B41" t="n">
-        <v>78061</v>
+        <v>92760</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>4365</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586636</v>
+        <v>586776</v>
       </c>
       <c r="R41" t="n">
-        <v>7090354</v>
+        <v>7090285</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4780,32 +4780,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128456473</v>
+        <v>128454373</v>
       </c>
       <c r="B43" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586959</v>
+        <v>586837</v>
       </c>
       <c r="R43" t="n">
-        <v>7090058</v>
+        <v>7090202</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128454373</v>
+        <v>128454343</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4888,21 +4888,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586837</v>
+        <v>586829</v>
       </c>
       <c r="R44" t="n">
-        <v>7090202</v>
+        <v>7090210</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128454343</v>
+        <v>128455049</v>
       </c>
       <c r="B45" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586829</v>
+        <v>586957</v>
       </c>
       <c r="R45" t="n">
-        <v>7090210</v>
+        <v>7090160</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5071,32 +5071,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128455049</v>
+        <v>128456473</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>92756</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586957</v>
+        <v>586959</v>
       </c>
       <c r="R46" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5944,32 +5944,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455876</v>
+        <v>128455902</v>
       </c>
       <c r="B55" t="n">
-        <v>78755</v>
+        <v>92756</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5982,7 +5982,7 @@
         <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090165</v>
+        <v>7090163</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6041,32 +6041,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128455902</v>
+        <v>128455941</v>
       </c>
       <c r="B56" t="n">
-        <v>92756</v>
+        <v>92750</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587083</v>
+        <v>587080</v>
       </c>
       <c r="R56" t="n">
-        <v>7090163</v>
+        <v>7090141</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,32 +6138,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128455941</v>
+        <v>128455058</v>
       </c>
       <c r="B57" t="n">
-        <v>92750</v>
+        <v>92756</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587080</v>
+        <v>586958</v>
       </c>
       <c r="R57" t="n">
-        <v>7090141</v>
+        <v>7090158</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128455058</v>
+        <v>128457035</v>
       </c>
       <c r="B58" t="n">
         <v>92756</v>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586958</v>
+        <v>586687</v>
       </c>
       <c r="R58" t="n">
-        <v>7090158</v>
+        <v>7090150</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6332,32 +6332,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128457035</v>
+        <v>128455876</v>
       </c>
       <c r="B59" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586687</v>
+        <v>587083</v>
       </c>
       <c r="R59" t="n">
-        <v>7090150</v>
+        <v>7090165</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128456020</v>
+        <v>128456801</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>91627</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587087</v>
+        <v>586808</v>
       </c>
       <c r="R9" t="n">
-        <v>7090081</v>
+        <v>7090047</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456801</v>
+        <v>128456020</v>
       </c>
       <c r="B10" t="n">
-        <v>91627</v>
+        <v>92756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586808</v>
+        <v>587087</v>
       </c>
       <c r="R10" t="n">
-        <v>7090047</v>
+        <v>7090081</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -2161,32 +2161,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R16" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,32 +2258,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B17" t="n">
-        <v>92784</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R17" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128453418</v>
+        <v>128452869</v>
       </c>
       <c r="B18" t="n">
-        <v>92756</v>
+        <v>80223</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586731</v>
+        <v>586682</v>
       </c>
       <c r="R18" t="n">
-        <v>7090285</v>
+        <v>7090334</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128452869</v>
+        <v>128453418</v>
       </c>
       <c r="B19" t="n">
-        <v>80223</v>
+        <v>92756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586682</v>
+        <v>586731</v>
       </c>
       <c r="R19" t="n">
-        <v>7090334</v>
+        <v>7090285</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2549,32 +2549,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456660</v>
+        <v>128454471</v>
       </c>
       <c r="B20" t="n">
-        <v>80222</v>
+        <v>78846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586916</v>
+        <v>586884</v>
       </c>
       <c r="R20" t="n">
-        <v>7090085</v>
+        <v>7090162</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2646,10 +2646,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128454471</v>
+        <v>128453928</v>
       </c>
       <c r="B21" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586884</v>
+        <v>586768</v>
       </c>
       <c r="R21" t="n">
-        <v>7090162</v>
+        <v>7090309</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,32 +2743,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128453928</v>
+        <v>128456660</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>80222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586768</v>
+        <v>586916</v>
       </c>
       <c r="R22" t="n">
-        <v>7090309</v>
+        <v>7090085</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2937,32 +2937,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128455293</v>
+        <v>128452701</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>92756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587050</v>
+        <v>586641</v>
       </c>
       <c r="R24" t="n">
-        <v>7090143</v>
+        <v>7090355</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128452844</v>
+        <v>128455293</v>
       </c>
       <c r="B25" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586675</v>
+        <v>587050</v>
       </c>
       <c r="R25" t="n">
-        <v>7090334</v>
+        <v>7090143</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456875</v>
+        <v>128452844</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>80194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586751</v>
+        <v>586675</v>
       </c>
       <c r="R26" t="n">
-        <v>7090092</v>
+        <v>7090334</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128452701</v>
+        <v>128456875</v>
       </c>
       <c r="B27" t="n">
-        <v>92756</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586641</v>
+        <v>586751</v>
       </c>
       <c r="R27" t="n">
-        <v>7090355</v>
+        <v>7090092</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4489,32 +4489,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128452657</v>
+        <v>128453864</v>
       </c>
       <c r="B40" t="n">
-        <v>78061</v>
+        <v>92760</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586636</v>
+        <v>586776</v>
       </c>
       <c r="R40" t="n">
-        <v>7090354</v>
+        <v>7090285</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4586,32 +4586,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128453864</v>
+        <v>128452657</v>
       </c>
       <c r="B41" t="n">
-        <v>92760</v>
+        <v>78061</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4365</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586776</v>
+        <v>586636</v>
       </c>
       <c r="R41" t="n">
-        <v>7090285</v>
+        <v>7090354</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128453795</v>
+        <v>128452749</v>
       </c>
       <c r="B50" t="n">
-        <v>78846</v>
+        <v>78755</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,21 +5470,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586761</v>
+        <v>586640</v>
       </c>
       <c r="R50" t="n">
-        <v>7090287</v>
+        <v>7090343</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128452749</v>
+        <v>128453795</v>
       </c>
       <c r="B51" t="n">
-        <v>78755</v>
+        <v>78846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,21 +5567,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586640</v>
+        <v>586761</v>
       </c>
       <c r="R51" t="n">
-        <v>7090343</v>
+        <v>7090287</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128456801</v>
+        <v>128453289</v>
       </c>
       <c r="B9" t="n">
-        <v>91627</v>
+        <v>91487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586808</v>
+        <v>586738</v>
       </c>
       <c r="R9" t="n">
-        <v>7090047</v>
+        <v>7090296</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1582,7 +1582,7 @@
         <v>128456020</v>
       </c>
       <c r="B10" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128453289</v>
+        <v>128456801</v>
       </c>
       <c r="B11" t="n">
-        <v>91486</v>
+        <v>91628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586738</v>
+        <v>586808</v>
       </c>
       <c r="R11" t="n">
-        <v>7090296</v>
+        <v>7090047</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1776,7 +1776,7 @@
         <v>128454030</v>
       </c>
       <c r="B12" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>128456148</v>
       </c>
       <c r="B13" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2161,32 +2161,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R16" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,32 +2258,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92785</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R17" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128452869</v>
+        <v>128453418</v>
       </c>
       <c r="B18" t="n">
-        <v>80223</v>
+        <v>92757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586682</v>
+        <v>586731</v>
       </c>
       <c r="R18" t="n">
-        <v>7090334</v>
+        <v>7090285</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128453418</v>
+        <v>128452869</v>
       </c>
       <c r="B19" t="n">
-        <v>92756</v>
+        <v>80223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586731</v>
+        <v>586682</v>
       </c>
       <c r="R19" t="n">
-        <v>7090285</v>
+        <v>7090334</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128454471</v>
+        <v>128453928</v>
       </c>
       <c r="B20" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586884</v>
+        <v>586768</v>
       </c>
       <c r="R20" t="n">
-        <v>7090162</v>
+        <v>7090309</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2646,32 +2646,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128453928</v>
+        <v>128456660</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>80222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586768</v>
+        <v>586916</v>
       </c>
       <c r="R21" t="n">
-        <v>7090309</v>
+        <v>7090085</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,32 +2743,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128456660</v>
+        <v>128454471</v>
       </c>
       <c r="B22" t="n">
-        <v>80222</v>
+        <v>78846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586916</v>
+        <v>586884</v>
       </c>
       <c r="R22" t="n">
-        <v>7090085</v>
+        <v>7090162</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2843,7 +2843,7 @@
         <v>128454384</v>
       </c>
       <c r="B23" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,32 +2937,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128452701</v>
+        <v>128455293</v>
       </c>
       <c r="B24" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586641</v>
+        <v>587050</v>
       </c>
       <c r="R24" t="n">
-        <v>7090355</v>
+        <v>7090143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128455293</v>
+        <v>128452844</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587050</v>
+        <v>586675</v>
       </c>
       <c r="R25" t="n">
-        <v>7090143</v>
+        <v>7090334</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128452844</v>
+        <v>128456875</v>
       </c>
       <c r="B26" t="n">
-        <v>80194</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586675</v>
+        <v>586751</v>
       </c>
       <c r="R26" t="n">
-        <v>7090334</v>
+        <v>7090092</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128456875</v>
+        <v>128452701</v>
       </c>
       <c r="B27" t="n">
-        <v>78846</v>
+        <v>92757</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586751</v>
+        <v>586641</v>
       </c>
       <c r="R27" t="n">
-        <v>7090092</v>
+        <v>7090355</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3328,7 +3328,7 @@
         <v>128455272</v>
       </c>
       <c r="B28" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128454846</v>
+        <v>128455546</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586924</v>
+        <v>587028</v>
       </c>
       <c r="R29" t="n">
-        <v>7090205</v>
+        <v>7090170</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128455546</v>
+        <v>128454846</v>
       </c>
       <c r="B30" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3530,21 +3530,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587028</v>
+        <v>586924</v>
       </c>
       <c r="R30" t="n">
-        <v>7090170</v>
+        <v>7090205</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3616,32 +3616,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128456386</v>
+        <v>128454639</v>
       </c>
       <c r="B31" t="n">
-        <v>92768</v>
+        <v>78755</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586982</v>
+        <v>586863</v>
       </c>
       <c r="R31" t="n">
-        <v>7090061</v>
+        <v>7090231</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,32 +3713,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128452918</v>
+        <v>128456612</v>
       </c>
       <c r="B32" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586693</v>
+        <v>586932</v>
       </c>
       <c r="R32" t="n">
-        <v>7090373</v>
+        <v>7090054</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128455740</v>
+        <v>128456454</v>
       </c>
       <c r="B33" t="n">
-        <v>92760</v>
+        <v>79708</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587055</v>
+        <v>586965</v>
       </c>
       <c r="R33" t="n">
-        <v>7090173</v>
+        <v>7090059</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128454639</v>
+        <v>128456386</v>
       </c>
       <c r="B34" t="n">
-        <v>78755</v>
+        <v>92769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586863</v>
+        <v>586982</v>
       </c>
       <c r="R34" t="n">
-        <v>7090231</v>
+        <v>7090061</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4004,32 +4004,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128456612</v>
+        <v>128455740</v>
       </c>
       <c r="B35" t="n">
-        <v>79708</v>
+        <v>92761</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586932</v>
+        <v>587055</v>
       </c>
       <c r="R35" t="n">
-        <v>7090054</v>
+        <v>7090173</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128456454</v>
+        <v>128452918</v>
       </c>
       <c r="B36" t="n">
-        <v>79708</v>
+        <v>92757</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586965</v>
+        <v>586693</v>
       </c>
       <c r="R36" t="n">
-        <v>7090059</v>
+        <v>7090373</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128454684</v>
+        <v>128452657</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>78061</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4209,21 +4209,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586912</v>
+        <v>586636</v>
       </c>
       <c r="R37" t="n">
-        <v>7090206</v>
+        <v>7090354</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4295,7 +4295,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128454512</v>
+        <v>128454684</v>
       </c>
       <c r="B38" t="n">
         <v>79089</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586853</v>
+        <v>586912</v>
       </c>
       <c r="R38" t="n">
-        <v>7090161</v>
+        <v>7090206</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128455537</v>
+        <v>128454512</v>
       </c>
       <c r="B39" t="n">
         <v>79089</v>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587026</v>
+        <v>586853</v>
       </c>
       <c r="R39" t="n">
-        <v>7090169</v>
+        <v>7090161</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4489,32 +4489,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128453864</v>
+        <v>128455537</v>
       </c>
       <c r="B40" t="n">
-        <v>92760</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586776</v>
+        <v>587026</v>
       </c>
       <c r="R40" t="n">
-        <v>7090285</v>
+        <v>7090169</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4586,32 +4586,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128452657</v>
+        <v>128453864</v>
       </c>
       <c r="B41" t="n">
-        <v>78061</v>
+        <v>92761</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>4365</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586636</v>
+        <v>586776</v>
       </c>
       <c r="R41" t="n">
-        <v>7090354</v>
+        <v>7090285</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128454343</v>
+        <v>128455049</v>
       </c>
       <c r="B44" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4888,21 +4888,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586829</v>
+        <v>586957</v>
       </c>
       <c r="R44" t="n">
-        <v>7090210</v>
+        <v>7090160</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128455049</v>
+        <v>128454343</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586957</v>
+        <v>586829</v>
       </c>
       <c r="R45" t="n">
-        <v>7090160</v>
+        <v>7090210</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5074,7 +5074,7 @@
         <v>128456473</v>
       </c>
       <c r="B46" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>128454991</v>
       </c>
       <c r="B47" t="n">
-        <v>91627</v>
+        <v>91628</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456539</v>
+        <v>128456368</v>
       </c>
       <c r="B48" t="n">
-        <v>92756</v>
+        <v>91432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,21 +5276,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586940</v>
+        <v>586986</v>
       </c>
       <c r="R48" t="n">
-        <v>7090064</v>
+        <v>7090055</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128456368</v>
+        <v>128456539</v>
       </c>
       <c r="B49" t="n">
-        <v>91431</v>
+        <v>92757</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586986</v>
+        <v>586940</v>
       </c>
       <c r="R49" t="n">
-        <v>7090055</v>
+        <v>7090064</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5656,7 +5656,7 @@
         <v>128453832</v>
       </c>
       <c r="B52" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>128456430</v>
       </c>
       <c r="B54" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,32 +5944,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455902</v>
+        <v>128455876</v>
       </c>
       <c r="B55" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5982,7 +5982,7 @@
         <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090163</v>
+        <v>7090165</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6041,10 +6041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128455941</v>
+        <v>128454284</v>
       </c>
       <c r="B56" t="n">
-        <v>92750</v>
+        <v>78846</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6052,21 +6052,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587080</v>
+        <v>586798</v>
       </c>
       <c r="R56" t="n">
-        <v>7090141</v>
+        <v>7090261</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,32 +6138,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128455058</v>
+        <v>128452666</v>
       </c>
       <c r="B57" t="n">
-        <v>92756</v>
+        <v>78846</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586958</v>
+        <v>586636</v>
       </c>
       <c r="R57" t="n">
-        <v>7090158</v>
+        <v>7090355</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6235,32 +6235,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128457035</v>
+        <v>128455941</v>
       </c>
       <c r="B58" t="n">
-        <v>92756</v>
+        <v>92751</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586687</v>
+        <v>587080</v>
       </c>
       <c r="R58" t="n">
-        <v>7090150</v>
+        <v>7090141</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6332,32 +6332,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455876</v>
+        <v>128455058</v>
       </c>
       <c r="B59" t="n">
-        <v>78755</v>
+        <v>92757</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587083</v>
+        <v>586958</v>
       </c>
       <c r="R59" t="n">
-        <v>7090165</v>
+        <v>7090158</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6429,32 +6429,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128454284</v>
+        <v>128455902</v>
       </c>
       <c r="B60" t="n">
-        <v>78846</v>
+        <v>92757</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586798</v>
+        <v>587083</v>
       </c>
       <c r="R60" t="n">
-        <v>7090261</v>
+        <v>7090163</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6526,32 +6526,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128452666</v>
+        <v>128457035</v>
       </c>
       <c r="B61" t="n">
-        <v>78846</v>
+        <v>92757</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586636</v>
+        <v>586687</v>
       </c>
       <c r="R61" t="n">
-        <v>7090355</v>
+        <v>7090150</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B62" t="n">
-        <v>78846</v>
+        <v>92757</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R62" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6720,32 +6720,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B63" t="n">
-        <v>92756</v>
+        <v>78846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R63" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B64" t="n">
-        <v>78755</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R64" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B65" t="n">
-        <v>79089</v>
+        <v>78755</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R65" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -3616,32 +3616,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128454639</v>
+        <v>128456386</v>
       </c>
       <c r="B31" t="n">
-        <v>78755</v>
+        <v>92769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586863</v>
+        <v>586982</v>
       </c>
       <c r="R31" t="n">
-        <v>7090231</v>
+        <v>7090061</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128456612</v>
+        <v>128454639</v>
       </c>
       <c r="B32" t="n">
-        <v>79708</v>
+        <v>78755</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3724,21 +3724,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586932</v>
+        <v>586863</v>
       </c>
       <c r="R32" t="n">
-        <v>7090054</v>
+        <v>7090231</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128456454</v>
+        <v>128456612</v>
       </c>
       <c r="B33" t="n">
         <v>79708</v>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586965</v>
+        <v>586932</v>
       </c>
       <c r="R33" t="n">
-        <v>7090059</v>
+        <v>7090054</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128456386</v>
+        <v>128456454</v>
       </c>
       <c r="B34" t="n">
-        <v>92769</v>
+        <v>79708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586982</v>
+        <v>586965</v>
       </c>
       <c r="R34" t="n">
-        <v>7090061</v>
+        <v>7090059</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128452657</v>
+        <v>128453864</v>
       </c>
       <c r="B37" t="n">
-        <v>78061</v>
+        <v>92761</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>4365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586636</v>
+        <v>586776</v>
       </c>
       <c r="R37" t="n">
-        <v>7090354</v>
+        <v>7090285</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128454684</v>
+        <v>128452657</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>78061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586912</v>
+        <v>586636</v>
       </c>
       <c r="R38" t="n">
-        <v>7090206</v>
+        <v>7090354</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128454512</v>
+        <v>128454684</v>
       </c>
       <c r="B39" t="n">
         <v>79089</v>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586853</v>
+        <v>586912</v>
       </c>
       <c r="R39" t="n">
-        <v>7090161</v>
+        <v>7090206</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4489,7 +4489,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128455537</v>
+        <v>128454512</v>
       </c>
       <c r="B40" t="n">
         <v>79089</v>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587026</v>
+        <v>586853</v>
       </c>
       <c r="R40" t="n">
-        <v>7090169</v>
+        <v>7090161</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4586,32 +4586,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128453864</v>
+        <v>128455537</v>
       </c>
       <c r="B41" t="n">
-        <v>92761</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586776</v>
+        <v>587026</v>
       </c>
       <c r="R41" t="n">
-        <v>7090285</v>
+        <v>7090169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128452749</v>
+        <v>128453795</v>
       </c>
       <c r="B50" t="n">
-        <v>78755</v>
+        <v>78846</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,21 +5470,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586640</v>
+        <v>586761</v>
       </c>
       <c r="R50" t="n">
-        <v>7090343</v>
+        <v>7090287</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128453795</v>
+        <v>128452749</v>
       </c>
       <c r="B51" t="n">
-        <v>78846</v>
+        <v>78755</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,21 +5567,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586761</v>
+        <v>586640</v>
       </c>
       <c r="R51" t="n">
-        <v>7090287</v>
+        <v>7090343</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>128454303</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>128456150</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128452297</v>
       </c>
       <c r="B8" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>128453289</v>
       </c>
       <c r="B9" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456020</v>
+        <v>128456801</v>
       </c>
       <c r="B10" t="n">
-        <v>92757</v>
+        <v>91655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587087</v>
+        <v>586808</v>
       </c>
       <c r="R10" t="n">
-        <v>7090081</v>
+        <v>7090047</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128456801</v>
+        <v>128456020</v>
       </c>
       <c r="B11" t="n">
-        <v>91628</v>
+        <v>92784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586808</v>
+        <v>587087</v>
       </c>
       <c r="R11" t="n">
-        <v>7090047</v>
+        <v>7090081</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1776,7 +1776,7 @@
         <v>128454030</v>
       </c>
       <c r="B12" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>128456148</v>
       </c>
       <c r="B13" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128456677</v>
+        <v>128453887</v>
       </c>
       <c r="B14" t="n">
-        <v>78755</v>
+        <v>79735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586919</v>
+        <v>586767</v>
       </c>
       <c r="R14" t="n">
-        <v>7090073</v>
+        <v>7090284</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128453887</v>
+        <v>128456677</v>
       </c>
       <c r="B15" t="n">
-        <v>79708</v>
+        <v>78782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586767</v>
+        <v>586919</v>
       </c>
       <c r="R15" t="n">
-        <v>7090284</v>
+        <v>7090073</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2161,32 +2161,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B16" t="n">
-        <v>92757</v>
+        <v>92812</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R16" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,32 +2258,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B17" t="n">
-        <v>92785</v>
+        <v>92784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R17" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128453418</v>
+        <v>128452869</v>
       </c>
       <c r="B18" t="n">
-        <v>92757</v>
+        <v>80250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586731</v>
+        <v>586682</v>
       </c>
       <c r="R18" t="n">
-        <v>7090285</v>
+        <v>7090334</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128452869</v>
+        <v>128453418</v>
       </c>
       <c r="B19" t="n">
-        <v>80223</v>
+        <v>92784</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586682</v>
+        <v>586731</v>
       </c>
       <c r="R19" t="n">
-        <v>7090334</v>
+        <v>7090285</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2549,32 +2549,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128453928</v>
+        <v>128454384</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>92784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586768</v>
+        <v>586835</v>
       </c>
       <c r="R20" t="n">
-        <v>7090309</v>
+        <v>7090189</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2646,32 +2646,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456660</v>
+        <v>128453928</v>
       </c>
       <c r="B21" t="n">
-        <v>80222</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586916</v>
+        <v>586768</v>
       </c>
       <c r="R21" t="n">
-        <v>7090085</v>
+        <v>7090309</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,32 +2743,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128454471</v>
+        <v>128456660</v>
       </c>
       <c r="B22" t="n">
-        <v>78846</v>
+        <v>80249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586884</v>
+        <v>586916</v>
       </c>
       <c r="R22" t="n">
-        <v>7090162</v>
+        <v>7090085</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,32 +2840,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128454384</v>
+        <v>128454471</v>
       </c>
       <c r="B23" t="n">
-        <v>92757</v>
+        <v>78873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586835</v>
+        <v>586884</v>
       </c>
       <c r="R23" t="n">
-        <v>7090189</v>
+        <v>7090162</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2937,32 +2937,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128455293</v>
+        <v>128452701</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>92784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587050</v>
+        <v>586641</v>
       </c>
       <c r="R24" t="n">
-        <v>7090143</v>
+        <v>7090355</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128452844</v>
+        <v>128455293</v>
       </c>
       <c r="B25" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586675</v>
+        <v>587050</v>
       </c>
       <c r="R25" t="n">
-        <v>7090334</v>
+        <v>7090143</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3131,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456875</v>
+        <v>128452844</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>80221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,21 +3142,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586751</v>
+        <v>586675</v>
       </c>
       <c r="R26" t="n">
-        <v>7090092</v>
+        <v>7090334</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128452701</v>
+        <v>128456875</v>
       </c>
       <c r="B27" t="n">
-        <v>92757</v>
+        <v>78873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586641</v>
+        <v>586751</v>
       </c>
       <c r="R27" t="n">
-        <v>7090355</v>
+        <v>7090092</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3328,7 +3328,7 @@
         <v>128455272</v>
       </c>
       <c r="B28" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128455546</v>
+        <v>128454846</v>
       </c>
       <c r="B29" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,21 +3433,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587028</v>
+        <v>586924</v>
       </c>
       <c r="R29" t="n">
-        <v>7090170</v>
+        <v>7090205</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128454846</v>
+        <v>128455546</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3530,21 +3530,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586924</v>
+        <v>587028</v>
       </c>
       <c r="R30" t="n">
-        <v>7090205</v>
+        <v>7090170</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128456386</v>
+        <v>128452918</v>
       </c>
       <c r="B31" t="n">
-        <v>92769</v>
+        <v>92784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586982</v>
+        <v>586693</v>
       </c>
       <c r="R31" t="n">
-        <v>7090061</v>
+        <v>7090373</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128454639</v>
+        <v>128456612</v>
       </c>
       <c r="B32" t="n">
-        <v>78755</v>
+        <v>79735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3724,21 +3724,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586863</v>
+        <v>586932</v>
       </c>
       <c r="R32" t="n">
-        <v>7090231</v>
+        <v>7090054</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128456612</v>
+        <v>128456454</v>
       </c>
       <c r="B33" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586932</v>
+        <v>586965</v>
       </c>
       <c r="R33" t="n">
-        <v>7090054</v>
+        <v>7090059</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128456454</v>
+        <v>128456386</v>
       </c>
       <c r="B34" t="n">
-        <v>79708</v>
+        <v>92796</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586965</v>
+        <v>586982</v>
       </c>
       <c r="R34" t="n">
-        <v>7090059</v>
+        <v>7090061</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4007,7 +4007,7 @@
         <v>128455740</v>
       </c>
       <c r="B35" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128452918</v>
+        <v>128454639</v>
       </c>
       <c r="B36" t="n">
-        <v>92757</v>
+        <v>78782</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586693</v>
+        <v>586863</v>
       </c>
       <c r="R36" t="n">
-        <v>7090373</v>
+        <v>7090231</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4201,7 +4201,7 @@
         <v>128453864</v>
       </c>
       <c r="B37" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128452657</v>
+        <v>128454684</v>
       </c>
       <c r="B38" t="n">
-        <v>78061</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586636</v>
+        <v>586912</v>
       </c>
       <c r="R38" t="n">
-        <v>7090354</v>
+        <v>7090206</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128454684</v>
+        <v>128454512</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586912</v>
+        <v>586853</v>
       </c>
       <c r="R39" t="n">
-        <v>7090206</v>
+        <v>7090161</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128454512</v>
+        <v>128452657</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>78088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586853</v>
+        <v>586636</v>
       </c>
       <c r="R40" t="n">
-        <v>7090161</v>
+        <v>7090354</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4589,7 +4589,7 @@
         <v>128455537</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,32 +4683,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128457243</v>
+        <v>128456473</v>
       </c>
       <c r="B42" t="n">
-        <v>78755</v>
+        <v>92784</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586620</v>
+        <v>586959</v>
       </c>
       <c r="R42" t="n">
-        <v>7090201</v>
+        <v>7090058</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128454373</v>
+        <v>128457243</v>
       </c>
       <c r="B43" t="n">
-        <v>79089</v>
+        <v>78782</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586837</v>
+        <v>586620</v>
       </c>
       <c r="R43" t="n">
-        <v>7090202</v>
+        <v>7090201</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128455049</v>
+        <v>128454373</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586957</v>
+        <v>586837</v>
       </c>
       <c r="R44" t="n">
-        <v>7090160</v>
+        <v>7090202</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4977,7 +4977,7 @@
         <v>128454343</v>
       </c>
       <c r="B45" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5071,32 +5071,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128456473</v>
+        <v>128455049</v>
       </c>
       <c r="B46" t="n">
-        <v>92757</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586959</v>
+        <v>586957</v>
       </c>
       <c r="R46" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5171,7 +5171,7 @@
         <v>128454991</v>
       </c>
       <c r="B47" t="n">
-        <v>91628</v>
+        <v>91655</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456368</v>
+        <v>128456539</v>
       </c>
       <c r="B48" t="n">
-        <v>91432</v>
+        <v>92784</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5276,21 +5276,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586986</v>
+        <v>586940</v>
       </c>
       <c r="R48" t="n">
-        <v>7090055</v>
+        <v>7090064</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128456539</v>
+        <v>128456368</v>
       </c>
       <c r="B49" t="n">
-        <v>92757</v>
+        <v>91459</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5373,21 +5373,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586940</v>
+        <v>586986</v>
       </c>
       <c r="R49" t="n">
-        <v>7090064</v>
+        <v>7090055</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128453795</v>
+        <v>128452749</v>
       </c>
       <c r="B50" t="n">
-        <v>78846</v>
+        <v>78782</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,21 +5470,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586761</v>
+        <v>586640</v>
       </c>
       <c r="R50" t="n">
-        <v>7090287</v>
+        <v>7090343</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5556,32 +5556,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128452749</v>
+        <v>128453832</v>
       </c>
       <c r="B51" t="n">
-        <v>78755</v>
+        <v>92784</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586640</v>
+        <v>586762</v>
       </c>
       <c r="R51" t="n">
-        <v>7090343</v>
+        <v>7090294</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5653,32 +5653,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128453832</v>
+        <v>128453795</v>
       </c>
       <c r="B52" t="n">
-        <v>92757</v>
+        <v>78873</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586762</v>
+        <v>586761</v>
       </c>
       <c r="R52" t="n">
-        <v>7090294</v>
+        <v>7090287</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5753,7 +5753,7 @@
         <v>128455401</v>
       </c>
       <c r="B53" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>128456430</v>
       </c>
       <c r="B54" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,10 +5944,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455876</v>
+        <v>128454284</v>
       </c>
       <c r="B55" t="n">
-        <v>78755</v>
+        <v>78873</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5955,21 +5955,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>587083</v>
+        <v>586798</v>
       </c>
       <c r="R55" t="n">
-        <v>7090165</v>
+        <v>7090261</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6041,10 +6041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128454284</v>
+        <v>128452666</v>
       </c>
       <c r="B56" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586798</v>
+        <v>586636</v>
       </c>
       <c r="R56" t="n">
-        <v>7090261</v>
+        <v>7090355</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128452666</v>
+        <v>128455876</v>
       </c>
       <c r="B57" t="n">
-        <v>78846</v>
+        <v>78782</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586636</v>
+        <v>587083</v>
       </c>
       <c r="R57" t="n">
-        <v>7090355</v>
+        <v>7090165</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6235,32 +6235,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128455941</v>
+        <v>128457035</v>
       </c>
       <c r="B58" t="n">
-        <v>92751</v>
+        <v>92784</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>587080</v>
+        <v>586687</v>
       </c>
       <c r="R58" t="n">
-        <v>7090141</v>
+        <v>7090150</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6332,32 +6332,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455058</v>
+        <v>128455941</v>
       </c>
       <c r="B59" t="n">
-        <v>92757</v>
+        <v>92778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586958</v>
+        <v>587080</v>
       </c>
       <c r="R59" t="n">
-        <v>7090158</v>
+        <v>7090141</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128455902</v>
+        <v>128455058</v>
       </c>
       <c r="B60" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>587083</v>
+        <v>586958</v>
       </c>
       <c r="R60" t="n">
-        <v>7090163</v>
+        <v>7090158</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6526,10 +6526,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128457035</v>
+        <v>128455902</v>
       </c>
       <c r="B61" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586687</v>
+        <v>587083</v>
       </c>
       <c r="R61" t="n">
-        <v>7090150</v>
+        <v>7090163</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B62" t="n">
-        <v>92757</v>
+        <v>78873</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R62" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6720,32 +6720,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B63" t="n">
-        <v>78846</v>
+        <v>92784</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R63" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B64" t="n">
-        <v>79089</v>
+        <v>78782</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R64" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B65" t="n">
-        <v>78755</v>
+        <v>79116</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R65" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128453289</v>
+        <v>128456801</v>
       </c>
       <c r="B9" t="n">
-        <v>91514</v>
+        <v>91655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586738</v>
+        <v>586808</v>
       </c>
       <c r="R9" t="n">
-        <v>7090296</v>
+        <v>7090047</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456801</v>
+        <v>128453289</v>
       </c>
       <c r="B10" t="n">
-        <v>91655</v>
+        <v>91514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586808</v>
+        <v>586738</v>
       </c>
       <c r="R10" t="n">
-        <v>7090047</v>
+        <v>7090296</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128453887</v>
+        <v>128456677</v>
       </c>
       <c r="B14" t="n">
-        <v>79735</v>
+        <v>78782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586767</v>
+        <v>586919</v>
       </c>
       <c r="R14" t="n">
-        <v>7090284</v>
+        <v>7090073</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128456677</v>
+        <v>128453887</v>
       </c>
       <c r="B15" t="n">
-        <v>78782</v>
+        <v>79735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586919</v>
+        <v>586767</v>
       </c>
       <c r="R15" t="n">
-        <v>7090073</v>
+        <v>7090284</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2161,32 +2161,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B16" t="n">
-        <v>92812</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R16" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,32 +2258,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B17" t="n">
-        <v>92784</v>
+        <v>92812</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R17" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2646,32 +2646,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128453928</v>
+        <v>128456660</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>80249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586768</v>
+        <v>586916</v>
       </c>
       <c r="R21" t="n">
-        <v>7090309</v>
+        <v>7090085</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,32 +2743,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128456660</v>
+        <v>128454471</v>
       </c>
       <c r="B22" t="n">
-        <v>80249</v>
+        <v>78873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586916</v>
+        <v>586884</v>
       </c>
       <c r="R22" t="n">
-        <v>7090085</v>
+        <v>7090162</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128454471</v>
+        <v>128453928</v>
       </c>
       <c r="B23" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586884</v>
+        <v>586768</v>
       </c>
       <c r="R23" t="n">
-        <v>7090162</v>
+        <v>7090309</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128452918</v>
+        <v>128456386</v>
       </c>
       <c r="B31" t="n">
-        <v>92784</v>
+        <v>92796</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586693</v>
+        <v>586982</v>
       </c>
       <c r="R31" t="n">
-        <v>7090373</v>
+        <v>7090061</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,32 +3713,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128456612</v>
+        <v>128452918</v>
       </c>
       <c r="B32" t="n">
-        <v>79735</v>
+        <v>92784</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586932</v>
+        <v>586693</v>
       </c>
       <c r="R32" t="n">
-        <v>7090054</v>
+        <v>7090373</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3810,32 +3810,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128456454</v>
+        <v>128455740</v>
       </c>
       <c r="B33" t="n">
-        <v>79735</v>
+        <v>92788</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586965</v>
+        <v>587055</v>
       </c>
       <c r="R33" t="n">
-        <v>7090059</v>
+        <v>7090173</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128456386</v>
+        <v>128454639</v>
       </c>
       <c r="B34" t="n">
-        <v>92796</v>
+        <v>78782</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586982</v>
+        <v>586863</v>
       </c>
       <c r="R34" t="n">
-        <v>7090061</v>
+        <v>7090231</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4004,32 +4004,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128455740</v>
+        <v>128456612</v>
       </c>
       <c r="B35" t="n">
-        <v>92788</v>
+        <v>79735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587055</v>
+        <v>586932</v>
       </c>
       <c r="R35" t="n">
-        <v>7090173</v>
+        <v>7090054</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128454639</v>
+        <v>128456454</v>
       </c>
       <c r="B36" t="n">
-        <v>78782</v>
+        <v>79735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4112,21 +4112,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586863</v>
+        <v>586965</v>
       </c>
       <c r="R36" t="n">
-        <v>7090231</v>
+        <v>7090059</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128454684</v>
+        <v>128452657</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>78088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586912</v>
+        <v>586636</v>
       </c>
       <c r="R38" t="n">
-        <v>7090206</v>
+        <v>7090354</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128454512</v>
+        <v>128454684</v>
       </c>
       <c r="B39" t="n">
         <v>79116</v>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586853</v>
+        <v>586912</v>
       </c>
       <c r="R39" t="n">
-        <v>7090161</v>
+        <v>7090206</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128452657</v>
+        <v>128454512</v>
       </c>
       <c r="B40" t="n">
-        <v>78088</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586636</v>
+        <v>586853</v>
       </c>
       <c r="R40" t="n">
-        <v>7090354</v>
+        <v>7090161</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4683,32 +4683,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128456473</v>
+        <v>128457243</v>
       </c>
       <c r="B42" t="n">
-        <v>92784</v>
+        <v>78782</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586959</v>
+        <v>586620</v>
       </c>
       <c r="R42" t="n">
-        <v>7090058</v>
+        <v>7090201</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128457243</v>
+        <v>128454373</v>
       </c>
       <c r="B43" t="n">
-        <v>78782</v>
+        <v>79116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586620</v>
+        <v>586837</v>
       </c>
       <c r="R43" t="n">
-        <v>7090201</v>
+        <v>7090202</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128454373</v>
+        <v>128454343</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4888,21 +4888,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586837</v>
+        <v>586829</v>
       </c>
       <c r="R44" t="n">
-        <v>7090202</v>
+        <v>7090210</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128454343</v>
+        <v>128455049</v>
       </c>
       <c r="B45" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586829</v>
+        <v>586957</v>
       </c>
       <c r="R45" t="n">
-        <v>7090210</v>
+        <v>7090160</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5071,32 +5071,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128455049</v>
+        <v>128456473</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>92784</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586957</v>
+        <v>586959</v>
       </c>
       <c r="R46" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5944,10 +5944,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128454284</v>
+        <v>128455876</v>
       </c>
       <c r="B55" t="n">
-        <v>78873</v>
+        <v>78782</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5955,21 +5955,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>586798</v>
+        <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090261</v>
+        <v>7090165</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6041,32 +6041,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128452666</v>
+        <v>128455902</v>
       </c>
       <c r="B56" t="n">
-        <v>78873</v>
+        <v>92784</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586636</v>
+        <v>587083</v>
       </c>
       <c r="R56" t="n">
-        <v>7090355</v>
+        <v>7090163</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128455876</v>
+        <v>128455941</v>
       </c>
       <c r="B57" t="n">
-        <v>78782</v>
+        <v>92778</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6149,21 +6149,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587083</v>
+        <v>587080</v>
       </c>
       <c r="R57" t="n">
-        <v>7090165</v>
+        <v>7090141</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128457035</v>
+        <v>128455058</v>
       </c>
       <c r="B58" t="n">
         <v>92784</v>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586687</v>
+        <v>586958</v>
       </c>
       <c r="R58" t="n">
-        <v>7090150</v>
+        <v>7090158</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6332,32 +6332,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455941</v>
+        <v>128457035</v>
       </c>
       <c r="B59" t="n">
-        <v>92778</v>
+        <v>92784</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587080</v>
+        <v>586687</v>
       </c>
       <c r="R59" t="n">
-        <v>7090141</v>
+        <v>7090150</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6429,32 +6429,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128455058</v>
+        <v>128454284</v>
       </c>
       <c r="B60" t="n">
-        <v>92784</v>
+        <v>78873</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586958</v>
+        <v>586798</v>
       </c>
       <c r="R60" t="n">
-        <v>7090158</v>
+        <v>7090261</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6526,32 +6526,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128455902</v>
+        <v>128452666</v>
       </c>
       <c r="B61" t="n">
-        <v>92784</v>
+        <v>78873</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>587083</v>
+        <v>586636</v>
       </c>
       <c r="R61" t="n">
-        <v>7090163</v>
+        <v>7090355</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6623,32 +6623,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B62" t="n">
-        <v>78873</v>
+        <v>92784</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R62" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6720,32 +6720,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B63" t="n">
-        <v>92784</v>
+        <v>78873</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R63" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>128454303</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128456150</v>
+        <v>128452297</v>
       </c>
       <c r="B7" t="n">
-        <v>78873</v>
+        <v>79739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587092</v>
+        <v>586593</v>
       </c>
       <c r="R7" t="n">
-        <v>7090041</v>
+        <v>7090373</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128452297</v>
+        <v>128456150</v>
       </c>
       <c r="B8" t="n">
-        <v>79735</v>
+        <v>78877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,21 +1396,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586593</v>
+        <v>587092</v>
       </c>
       <c r="R8" t="n">
-        <v>7090373</v>
+        <v>7090041</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1485,7 +1485,7 @@
         <v>128456801</v>
       </c>
       <c r="B9" t="n">
-        <v>91655</v>
+        <v>91665</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128453289</v>
+        <v>128456020</v>
       </c>
       <c r="B10" t="n">
-        <v>91514</v>
+        <v>92794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586738</v>
+        <v>587087</v>
       </c>
       <c r="R10" t="n">
-        <v>7090296</v>
+        <v>7090081</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128456020</v>
+        <v>128453289</v>
       </c>
       <c r="B11" t="n">
-        <v>92784</v>
+        <v>91524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587087</v>
+        <v>586738</v>
       </c>
       <c r="R11" t="n">
-        <v>7090081</v>
+        <v>7090296</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1776,7 +1776,7 @@
         <v>128454030</v>
       </c>
       <c r="B12" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>128456148</v>
       </c>
       <c r="B13" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128456677</v>
       </c>
       <c r="B14" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>128453887</v>
       </c>
       <c r="B15" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>128454707</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>128455756</v>
       </c>
       <c r="B17" t="n">
-        <v>92812</v>
+        <v>92823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2271,12 @@
       <c r="E17" t="n">
         <v>5449</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2355,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128452869</v>
+        <v>128453418</v>
       </c>
       <c r="B18" t="n">
-        <v>80250</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,21 +2357,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586682</v>
+        <v>586731</v>
       </c>
       <c r="R18" t="n">
-        <v>7090334</v>
+        <v>7090285</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128453418</v>
+        <v>128452869</v>
       </c>
       <c r="B19" t="n">
-        <v>92784</v>
+        <v>80254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2487,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586731</v>
+        <v>586682</v>
       </c>
       <c r="R19" t="n">
-        <v>7090285</v>
+        <v>7090334</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2552,7 +2543,7 @@
         <v>128454384</v>
       </c>
       <c r="B20" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,32 +2637,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456660</v>
+        <v>128453928</v>
       </c>
       <c r="B21" t="n">
-        <v>80249</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586916</v>
+        <v>586768</v>
       </c>
       <c r="R21" t="n">
-        <v>7090085</v>
+        <v>7090309</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2746,7 +2737,7 @@
         <v>128454471</v>
       </c>
       <c r="B22" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,32 +2831,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128453928</v>
+        <v>128456660</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>80253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586768</v>
+        <v>586916</v>
       </c>
       <c r="R23" t="n">
-        <v>7090309</v>
+        <v>7090085</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2940,7 +2931,7 @@
         <v>128452701</v>
       </c>
       <c r="B24" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3028,7 @@
         <v>128455293</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,10 +3122,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128452844</v>
+        <v>128456875</v>
       </c>
       <c r="B26" t="n">
-        <v>80221</v>
+        <v>78877</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,21 +3133,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586675</v>
+        <v>586751</v>
       </c>
       <c r="R26" t="n">
-        <v>7090334</v>
+        <v>7090092</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3228,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128456875</v>
+        <v>128452844</v>
       </c>
       <c r="B27" t="n">
-        <v>78873</v>
+        <v>80225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,21 +3230,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3263,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586751</v>
+        <v>586675</v>
       </c>
       <c r="R27" t="n">
-        <v>7090092</v>
+        <v>7090334</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3328,7 +3319,7 @@
         <v>128455272</v>
       </c>
       <c r="B28" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3425,7 +3416,7 @@
         <v>128454846</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,7 +3513,7 @@
         <v>128455546</v>
       </c>
       <c r="B30" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3616,32 +3607,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128456386</v>
+        <v>128456454</v>
       </c>
       <c r="B31" t="n">
-        <v>92796</v>
+        <v>79739</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3651,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586982</v>
+        <v>586965</v>
       </c>
       <c r="R31" t="n">
-        <v>7090061</v>
+        <v>7090059</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128452918</v>
+        <v>128456612</v>
       </c>
       <c r="B32" t="n">
-        <v>92784</v>
+        <v>79739</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3748,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586693</v>
+        <v>586932</v>
       </c>
       <c r="R32" t="n">
-        <v>7090373</v>
+        <v>7090054</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3810,32 +3801,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128455740</v>
+        <v>128456386</v>
       </c>
       <c r="B33" t="n">
-        <v>92788</v>
+        <v>92806</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587055</v>
+        <v>586982</v>
       </c>
       <c r="R33" t="n">
-        <v>7090173</v>
+        <v>7090061</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3907,32 +3898,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128454639</v>
+        <v>128452918</v>
       </c>
       <c r="B34" t="n">
-        <v>78782</v>
+        <v>92794</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3942,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586863</v>
+        <v>586693</v>
       </c>
       <c r="R34" t="n">
-        <v>7090231</v>
+        <v>7090373</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4004,32 +3995,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128456612</v>
+        <v>128455740</v>
       </c>
       <c r="B35" t="n">
-        <v>79735</v>
+        <v>92798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4039,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586932</v>
+        <v>587055</v>
       </c>
       <c r="R35" t="n">
-        <v>7090054</v>
+        <v>7090173</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,10 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128456454</v>
+        <v>128454639</v>
       </c>
       <c r="B36" t="n">
-        <v>79735</v>
+        <v>78786</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4112,21 +4103,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4136,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586965</v>
+        <v>586863</v>
       </c>
       <c r="R36" t="n">
-        <v>7090059</v>
+        <v>7090231</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4201,7 +4192,7 @@
         <v>128453864</v>
       </c>
       <c r="B37" t="n">
-        <v>92788</v>
+        <v>92798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4295,10 +4286,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128452657</v>
+        <v>128454512</v>
       </c>
       <c r="B38" t="n">
-        <v>78088</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4306,21 +4297,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4330,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586636</v>
+        <v>586853</v>
       </c>
       <c r="R38" t="n">
-        <v>7090354</v>
+        <v>7090161</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4395,7 +4386,7 @@
         <v>128454684</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4489,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128454512</v>
+        <v>128455537</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4524,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586853</v>
+        <v>587026</v>
       </c>
       <c r="R40" t="n">
-        <v>7090161</v>
+        <v>7090169</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4586,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128455537</v>
+        <v>128452657</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>78092</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4597,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4621,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587026</v>
+        <v>586636</v>
       </c>
       <c r="R41" t="n">
-        <v>7090169</v>
+        <v>7090354</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4683,10 +4674,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128457243</v>
+        <v>128454343</v>
       </c>
       <c r="B42" t="n">
-        <v>78782</v>
+        <v>78877</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4694,21 +4685,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4718,10 +4709,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586620</v>
+        <v>586829</v>
       </c>
       <c r="R42" t="n">
-        <v>7090201</v>
+        <v>7090210</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4780,32 +4771,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128454373</v>
+        <v>128456473</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>92794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4815,10 +4806,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586837</v>
+        <v>586959</v>
       </c>
       <c r="R43" t="n">
-        <v>7090202</v>
+        <v>7090058</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4877,10 +4868,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128454343</v>
+        <v>128457243</v>
       </c>
       <c r="B44" t="n">
-        <v>78873</v>
+        <v>78786</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4888,21 +4879,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4912,10 +4903,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586829</v>
+        <v>586620</v>
       </c>
       <c r="R44" t="n">
-        <v>7090210</v>
+        <v>7090201</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4977,7 +4968,7 @@
         <v>128455049</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5071,32 +5062,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128456473</v>
+        <v>128454373</v>
       </c>
       <c r="B46" t="n">
-        <v>92784</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5106,10 +5097,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586959</v>
+        <v>586837</v>
       </c>
       <c r="R46" t="n">
-        <v>7090058</v>
+        <v>7090202</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5171,7 +5162,7 @@
         <v>128454991</v>
       </c>
       <c r="B47" t="n">
-        <v>91655</v>
+        <v>91665</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5268,7 +5259,7 @@
         <v>128456539</v>
       </c>
       <c r="B48" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5365,7 +5356,7 @@
         <v>128456368</v>
       </c>
       <c r="B49" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5459,32 +5450,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128452749</v>
+        <v>128453832</v>
       </c>
       <c r="B50" t="n">
-        <v>78782</v>
+        <v>92794</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5494,10 +5485,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586640</v>
+        <v>586762</v>
       </c>
       <c r="R50" t="n">
-        <v>7090343</v>
+        <v>7090294</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5556,32 +5547,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128453832</v>
+        <v>128452749</v>
       </c>
       <c r="B51" t="n">
-        <v>92784</v>
+        <v>78786</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5591,10 +5582,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586762</v>
+        <v>586640</v>
       </c>
       <c r="R51" t="n">
-        <v>7090294</v>
+        <v>7090343</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5656,7 +5647,7 @@
         <v>128453795</v>
       </c>
       <c r="B52" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5750,10 +5741,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128455401</v>
+        <v>128456430</v>
       </c>
       <c r="B53" t="n">
-        <v>78782</v>
+        <v>92823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5761,23 +5752,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5785,10 +5767,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>587046</v>
+        <v>586964</v>
       </c>
       <c r="R53" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5847,10 +5829,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128456430</v>
+        <v>128455401</v>
       </c>
       <c r="B54" t="n">
-        <v>92812</v>
+        <v>78786</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5858,21 +5840,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5882,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586964</v>
+        <v>587046</v>
       </c>
       <c r="R54" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5947,7 +5929,7 @@
         <v>128455876</v>
       </c>
       <c r="B55" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6041,32 +6023,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128455902</v>
+        <v>128452666</v>
       </c>
       <c r="B56" t="n">
-        <v>92784</v>
+        <v>78877</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6076,10 +6058,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587083</v>
+        <v>586636</v>
       </c>
       <c r="R56" t="n">
-        <v>7090163</v>
+        <v>7090355</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6138,10 +6120,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128455941</v>
+        <v>128454284</v>
       </c>
       <c r="B57" t="n">
-        <v>92778</v>
+        <v>78877</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6149,21 +6131,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6173,10 +6155,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587080</v>
+        <v>586798</v>
       </c>
       <c r="R57" t="n">
-        <v>7090141</v>
+        <v>7090261</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6235,10 +6217,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128455058</v>
+        <v>128455902</v>
       </c>
       <c r="B58" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6270,10 +6252,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586958</v>
+        <v>587083</v>
       </c>
       <c r="R58" t="n">
-        <v>7090158</v>
+        <v>7090163</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6332,32 +6314,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128457035</v>
+        <v>128455941</v>
       </c>
       <c r="B59" t="n">
-        <v>92784</v>
+        <v>92788</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6367,10 +6349,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586687</v>
+        <v>587080</v>
       </c>
       <c r="R59" t="n">
-        <v>7090150</v>
+        <v>7090141</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6429,32 +6411,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128454284</v>
+        <v>128455058</v>
       </c>
       <c r="B60" t="n">
-        <v>78873</v>
+        <v>92794</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6464,10 +6446,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586798</v>
+        <v>586958</v>
       </c>
       <c r="R60" t="n">
-        <v>7090261</v>
+        <v>7090158</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6526,32 +6508,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128452666</v>
+        <v>128457035</v>
       </c>
       <c r="B61" t="n">
-        <v>78873</v>
+        <v>92794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6543,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586636</v>
+        <v>586687</v>
       </c>
       <c r="R61" t="n">
-        <v>7090355</v>
+        <v>7090150</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6623,32 +6605,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B62" t="n">
-        <v>92784</v>
+        <v>78877</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6658,10 +6640,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R62" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6720,32 +6702,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B63" t="n">
-        <v>78873</v>
+        <v>92794</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6737,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R63" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6817,10 +6799,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B64" t="n">
-        <v>78782</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6810,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6834,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R64" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6914,10 +6896,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B65" t="n">
-        <v>79116</v>
+        <v>78786</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6925,21 +6907,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6949,10 +6931,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R65" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1288,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128452297</v>
+        <v>128456150</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586593</v>
+        <v>587092</v>
       </c>
       <c r="R7" t="n">
-        <v>7090373</v>
+        <v>7090041</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128456150</v>
+        <v>128452297</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,21 +1396,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587092</v>
+        <v>586593</v>
       </c>
       <c r="R8" t="n">
-        <v>7090041</v>
+        <v>7090373</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128456801</v>
+        <v>128453289</v>
       </c>
       <c r="B9" t="n">
-        <v>91665</v>
+        <v>91524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586808</v>
+        <v>586738</v>
       </c>
       <c r="R9" t="n">
-        <v>7090047</v>
+        <v>7090296</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128453289</v>
+        <v>128456801</v>
       </c>
       <c r="B11" t="n">
-        <v>91524</v>
+        <v>91665</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586738</v>
+        <v>586808</v>
       </c>
       <c r="R11" t="n">
-        <v>7090296</v>
+        <v>7090047</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2161,34 +2161,25 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B16" t="n">
-        <v>92794</v>
+        <v>92823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2196,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R16" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,25 +2249,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B17" t="n">
-        <v>92823</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R17" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2540,32 +2540,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128454384</v>
+        <v>128454471</v>
       </c>
       <c r="B20" t="n">
-        <v>92794</v>
+        <v>78877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586835</v>
+        <v>586884</v>
       </c>
       <c r="R20" t="n">
-        <v>7090189</v>
+        <v>7090162</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2734,32 +2734,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128454471</v>
+        <v>128456660</v>
       </c>
       <c r="B22" t="n">
-        <v>78877</v>
+        <v>80253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586884</v>
+        <v>586916</v>
       </c>
       <c r="R22" t="n">
-        <v>7090162</v>
+        <v>7090085</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128456660</v>
+        <v>128454384</v>
       </c>
       <c r="B23" t="n">
-        <v>80253</v>
+        <v>92794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586916</v>
+        <v>586835</v>
       </c>
       <c r="R23" t="n">
-        <v>7090085</v>
+        <v>7090189</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128456454</v>
+        <v>128454639</v>
       </c>
       <c r="B31" t="n">
-        <v>79739</v>
+        <v>78786</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586965</v>
+        <v>586863</v>
       </c>
       <c r="R31" t="n">
-        <v>7090059</v>
+        <v>7090231</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128456612</v>
+        <v>128456386</v>
       </c>
       <c r="B32" t="n">
-        <v>79739</v>
+        <v>92806</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586932</v>
+        <v>586982</v>
       </c>
       <c r="R32" t="n">
-        <v>7090054</v>
+        <v>7090061</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128456386</v>
+        <v>128452918</v>
       </c>
       <c r="B33" t="n">
-        <v>92806</v>
+        <v>92794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,21 +3812,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586982</v>
+        <v>586693</v>
       </c>
       <c r="R33" t="n">
-        <v>7090061</v>
+        <v>7090373</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3898,32 +3898,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128452918</v>
+        <v>128455740</v>
       </c>
       <c r="B34" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586693</v>
+        <v>587055</v>
       </c>
       <c r="R34" t="n">
-        <v>7090373</v>
+        <v>7090173</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3995,32 +3995,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128455740</v>
+        <v>128456612</v>
       </c>
       <c r="B35" t="n">
-        <v>92798</v>
+        <v>79739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587055</v>
+        <v>586932</v>
       </c>
       <c r="R35" t="n">
-        <v>7090173</v>
+        <v>7090054</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4092,10 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128454639</v>
+        <v>128456454</v>
       </c>
       <c r="B36" t="n">
-        <v>78786</v>
+        <v>79739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4103,21 +4103,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586863</v>
+        <v>586965</v>
       </c>
       <c r="R36" t="n">
-        <v>7090231</v>
+        <v>7090059</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128454512</v>
+        <v>128452657</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>78092</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4297,21 +4297,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586853</v>
+        <v>586636</v>
       </c>
       <c r="R38" t="n">
-        <v>7090161</v>
+        <v>7090354</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4480,7 +4480,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128455537</v>
+        <v>128454512</v>
       </c>
       <c r="B40" t="n">
         <v>79120</v>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587026</v>
+        <v>586853</v>
       </c>
       <c r="R40" t="n">
-        <v>7090169</v>
+        <v>7090161</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128452657</v>
+        <v>128455537</v>
       </c>
       <c r="B41" t="n">
-        <v>78092</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586636</v>
+        <v>587026</v>
       </c>
       <c r="R41" t="n">
-        <v>7090354</v>
+        <v>7090169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4674,10 +4674,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128454343</v>
+        <v>128454373</v>
       </c>
       <c r="B42" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4685,21 +4685,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586829</v>
+        <v>586837</v>
       </c>
       <c r="R42" t="n">
-        <v>7090210</v>
+        <v>7090202</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,32 +4771,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128456473</v>
+        <v>128454343</v>
       </c>
       <c r="B43" t="n">
-        <v>92794</v>
+        <v>78877</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586959</v>
+        <v>586829</v>
       </c>
       <c r="R43" t="n">
-        <v>7090058</v>
+        <v>7090210</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128457243</v>
+        <v>128455049</v>
       </c>
       <c r="B44" t="n">
-        <v>78786</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,21 +4879,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586620</v>
+        <v>586957</v>
       </c>
       <c r="R44" t="n">
-        <v>7090201</v>
+        <v>7090160</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4965,32 +4965,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128455049</v>
+        <v>128456473</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>92794</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586957</v>
+        <v>586959</v>
       </c>
       <c r="R45" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5062,10 +5062,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128454373</v>
+        <v>128457243</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>78786</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586837</v>
+        <v>586620</v>
       </c>
       <c r="R46" t="n">
-        <v>7090202</v>
+        <v>7090201</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5159,32 +5159,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128454991</v>
+        <v>128456539</v>
       </c>
       <c r="B47" t="n">
-        <v>91665</v>
+        <v>92794</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586930</v>
+        <v>586940</v>
       </c>
       <c r="R47" t="n">
-        <v>7090184</v>
+        <v>7090064</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456539</v>
+        <v>128456368</v>
       </c>
       <c r="B48" t="n">
-        <v>92794</v>
+        <v>91469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5267,21 +5267,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586940</v>
+        <v>586986</v>
       </c>
       <c r="R48" t="n">
-        <v>7090064</v>
+        <v>7090055</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5353,32 +5353,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128456368</v>
+        <v>128454991</v>
       </c>
       <c r="B49" t="n">
-        <v>91469</v>
+        <v>91665</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586986</v>
+        <v>586930</v>
       </c>
       <c r="R49" t="n">
-        <v>7090055</v>
+        <v>7090184</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5926,32 +5926,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455876</v>
+        <v>128455902</v>
       </c>
       <c r="B55" t="n">
-        <v>78786</v>
+        <v>92794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5964,7 +5964,7 @@
         <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090165</v>
+        <v>7090163</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6023,10 +6023,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128452666</v>
+        <v>128455941</v>
       </c>
       <c r="B56" t="n">
-        <v>78877</v>
+        <v>92788</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6034,21 +6034,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586636</v>
+        <v>587080</v>
       </c>
       <c r="R56" t="n">
-        <v>7090355</v>
+        <v>7090141</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6120,32 +6120,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128454284</v>
+        <v>128455058</v>
       </c>
       <c r="B57" t="n">
-        <v>78877</v>
+        <v>92794</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586798</v>
+        <v>586958</v>
       </c>
       <c r="R57" t="n">
-        <v>7090261</v>
+        <v>7090158</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128455902</v>
+        <v>128457035</v>
       </c>
       <c r="B58" t="n">
         <v>92794</v>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>587083</v>
+        <v>586687</v>
       </c>
       <c r="R58" t="n">
-        <v>7090163</v>
+        <v>7090150</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6314,10 +6314,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455941</v>
+        <v>128455876</v>
       </c>
       <c r="B59" t="n">
-        <v>92788</v>
+        <v>78786</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587080</v>
+        <v>587083</v>
       </c>
       <c r="R59" t="n">
-        <v>7090141</v>
+        <v>7090165</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6411,32 +6411,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128455058</v>
+        <v>128454284</v>
       </c>
       <c r="B60" t="n">
-        <v>92794</v>
+        <v>78877</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586958</v>
+        <v>586798</v>
       </c>
       <c r="R60" t="n">
-        <v>7090158</v>
+        <v>7090261</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6508,32 +6508,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128457035</v>
+        <v>128452666</v>
       </c>
       <c r="B61" t="n">
-        <v>92794</v>
+        <v>78877</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586687</v>
+        <v>586636</v>
       </c>
       <c r="R61" t="n">
-        <v>7090150</v>
+        <v>7090355</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6605,32 +6605,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B62" t="n">
-        <v>78877</v>
+        <v>92794</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R62" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6702,32 +6702,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B63" t="n">
-        <v>92794</v>
+        <v>78877</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R63" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6799,10 +6799,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>78786</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R64" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6896,10 +6896,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B65" t="n">
-        <v>78786</v>
+        <v>79120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6907,21 +6907,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R65" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1191,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128454303</v>
+        <v>128452297</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,21 +1202,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586789</v>
+        <v>586593</v>
       </c>
       <c r="R6" t="n">
-        <v>7090238</v>
+        <v>7090373</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128456150</v>
+        <v>128454303</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587092</v>
+        <v>586789</v>
       </c>
       <c r="R7" t="n">
-        <v>7090041</v>
+        <v>7090238</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128452297</v>
+        <v>128456150</v>
       </c>
       <c r="B8" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,21 +1396,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586593</v>
+        <v>587092</v>
       </c>
       <c r="R8" t="n">
-        <v>7090373</v>
+        <v>7090041</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128453418</v>
+        <v>128452869</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>80254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,21 +2357,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586731</v>
+        <v>586682</v>
       </c>
       <c r="R18" t="n">
-        <v>7090285</v>
+        <v>7090334</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2443,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128452869</v>
+        <v>128453418</v>
       </c>
       <c r="B19" t="n">
-        <v>80254</v>
+        <v>92794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586682</v>
+        <v>586731</v>
       </c>
       <c r="R19" t="n">
-        <v>7090334</v>
+        <v>7090285</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2540,32 +2540,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128454471</v>
+        <v>128454384</v>
       </c>
       <c r="B20" t="n">
-        <v>78877</v>
+        <v>92794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586884</v>
+        <v>586835</v>
       </c>
       <c r="R20" t="n">
-        <v>7090162</v>
+        <v>7090189</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128453928</v>
+        <v>128454471</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586768</v>
+        <v>586884</v>
       </c>
       <c r="R21" t="n">
-        <v>7090309</v>
+        <v>7090162</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2734,32 +2734,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128456660</v>
+        <v>128453928</v>
       </c>
       <c r="B22" t="n">
-        <v>80253</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586916</v>
+        <v>586768</v>
       </c>
       <c r="R22" t="n">
-        <v>7090085</v>
+        <v>7090309</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128454384</v>
+        <v>128456660</v>
       </c>
       <c r="B23" t="n">
-        <v>92794</v>
+        <v>80253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586835</v>
+        <v>586916</v>
       </c>
       <c r="R23" t="n">
-        <v>7090189</v>
+        <v>7090085</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128456539</v>
+        <v>128456368</v>
       </c>
       <c r="B47" t="n">
-        <v>92794</v>
+        <v>91469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5170,21 +5170,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586940</v>
+        <v>586986</v>
       </c>
       <c r="R47" t="n">
-        <v>7090064</v>
+        <v>7090055</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456368</v>
+        <v>128456539</v>
       </c>
       <c r="B48" t="n">
-        <v>91469</v>
+        <v>92794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5267,21 +5267,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586986</v>
+        <v>586940</v>
       </c>
       <c r="R48" t="n">
-        <v>7090055</v>
+        <v>7090064</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1191,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128452297</v>
+        <v>128454303</v>
       </c>
       <c r="B6" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,21 +1202,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586593</v>
+        <v>586789</v>
       </c>
       <c r="R6" t="n">
-        <v>7090373</v>
+        <v>7090238</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128454303</v>
+        <v>128452297</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586789</v>
+        <v>586593</v>
       </c>
       <c r="R7" t="n">
-        <v>7090238</v>
+        <v>7090373</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128453289</v>
+        <v>128456020</v>
       </c>
       <c r="B9" t="n">
-        <v>91524</v>
+        <v>92794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586738</v>
+        <v>587087</v>
       </c>
       <c r="R9" t="n">
-        <v>7090296</v>
+        <v>7090081</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456020</v>
+        <v>128456801</v>
       </c>
       <c r="B10" t="n">
-        <v>92794</v>
+        <v>91665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587087</v>
+        <v>586808</v>
       </c>
       <c r="R10" t="n">
-        <v>7090081</v>
+        <v>7090047</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128456801</v>
+        <v>128453289</v>
       </c>
       <c r="B11" t="n">
-        <v>91665</v>
+        <v>91524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586808</v>
+        <v>586738</v>
       </c>
       <c r="R11" t="n">
-        <v>7090047</v>
+        <v>7090296</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128454030</v>
+        <v>128456148</v>
       </c>
       <c r="B12" t="n">
         <v>92794</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586773</v>
+        <v>587092</v>
       </c>
       <c r="R12" t="n">
-        <v>7090298</v>
+        <v>7090041</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128456148</v>
+        <v>128454030</v>
       </c>
       <c r="B13" t="n">
         <v>92794</v>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587092</v>
+        <v>586773</v>
       </c>
       <c r="R13" t="n">
-        <v>7090041</v>
+        <v>7090298</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2161,25 +2161,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B16" t="n">
-        <v>92823</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2187,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R16" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2249,34 +2258,25 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>92823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R17" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128452869</v>
+        <v>128453418</v>
       </c>
       <c r="B18" t="n">
-        <v>80254</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,21 +2357,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586682</v>
+        <v>586731</v>
       </c>
       <c r="R18" t="n">
-        <v>7090334</v>
+        <v>7090285</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2443,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128453418</v>
+        <v>128452869</v>
       </c>
       <c r="B19" t="n">
-        <v>92794</v>
+        <v>80254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586731</v>
+        <v>586682</v>
       </c>
       <c r="R19" t="n">
-        <v>7090285</v>
+        <v>7090334</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2540,32 +2540,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128454384</v>
+        <v>128454471</v>
       </c>
       <c r="B20" t="n">
-        <v>92794</v>
+        <v>78877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586835</v>
+        <v>586884</v>
       </c>
       <c r="R20" t="n">
-        <v>7090189</v>
+        <v>7090162</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2637,32 +2637,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128454471</v>
+        <v>128456660</v>
       </c>
       <c r="B21" t="n">
-        <v>78877</v>
+        <v>80253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586884</v>
+        <v>586916</v>
       </c>
       <c r="R21" t="n">
-        <v>7090162</v>
+        <v>7090085</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2734,32 +2734,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128453928</v>
+        <v>128454384</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>92794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586768</v>
+        <v>586835</v>
       </c>
       <c r="R22" t="n">
-        <v>7090309</v>
+        <v>7090189</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2831,32 +2831,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128456660</v>
+        <v>128453928</v>
       </c>
       <c r="B23" t="n">
-        <v>80253</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586916</v>
+        <v>586768</v>
       </c>
       <c r="R23" t="n">
-        <v>7090085</v>
+        <v>7090309</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128455293</v>
+        <v>128456875</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,21 +3036,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587050</v>
+        <v>586751</v>
       </c>
       <c r="R25" t="n">
-        <v>7090143</v>
+        <v>7090092</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128456875</v>
+        <v>128452844</v>
       </c>
       <c r="B26" t="n">
-        <v>78877</v>
+        <v>80225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,21 +3133,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586751</v>
+        <v>586675</v>
       </c>
       <c r="R26" t="n">
-        <v>7090092</v>
+        <v>7090334</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128452844</v>
+        <v>128455293</v>
       </c>
       <c r="B27" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586675</v>
+        <v>587050</v>
       </c>
       <c r="R27" t="n">
-        <v>7090334</v>
+        <v>7090143</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3607,32 +3607,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128454639</v>
+        <v>128456386</v>
       </c>
       <c r="B31" t="n">
-        <v>78786</v>
+        <v>92806</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586863</v>
+        <v>586982</v>
       </c>
       <c r="R31" t="n">
-        <v>7090231</v>
+        <v>7090061</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128456386</v>
+        <v>128455740</v>
       </c>
       <c r="B32" t="n">
-        <v>92806</v>
+        <v>92798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586982</v>
+        <v>587055</v>
       </c>
       <c r="R32" t="n">
-        <v>7090061</v>
+        <v>7090173</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3801,32 +3801,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128452918</v>
+        <v>128456454</v>
       </c>
       <c r="B33" t="n">
-        <v>92794</v>
+        <v>79739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586693</v>
+        <v>586965</v>
       </c>
       <c r="R33" t="n">
-        <v>7090373</v>
+        <v>7090059</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3898,32 +3898,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128455740</v>
+        <v>128456612</v>
       </c>
       <c r="B34" t="n">
-        <v>92798</v>
+        <v>79739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587055</v>
+        <v>586932</v>
       </c>
       <c r="R34" t="n">
-        <v>7090173</v>
+        <v>7090054</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128456612</v>
+        <v>128454639</v>
       </c>
       <c r="B35" t="n">
-        <v>79739</v>
+        <v>78786</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586932</v>
+        <v>586863</v>
       </c>
       <c r="R35" t="n">
-        <v>7090054</v>
+        <v>7090231</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4092,32 +4092,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128456454</v>
+        <v>128452918</v>
       </c>
       <c r="B36" t="n">
-        <v>79739</v>
+        <v>92794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586965</v>
+        <v>586693</v>
       </c>
       <c r="R36" t="n">
-        <v>7090059</v>
+        <v>7090373</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4674,32 +4674,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128454373</v>
+        <v>128456473</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>92794</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586837</v>
+        <v>586959</v>
       </c>
       <c r="R42" t="n">
-        <v>7090202</v>
+        <v>7090058</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128454343</v>
+        <v>128457243</v>
       </c>
       <c r="B43" t="n">
-        <v>78877</v>
+        <v>78786</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586829</v>
+        <v>586620</v>
       </c>
       <c r="R43" t="n">
-        <v>7090210</v>
+        <v>7090201</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128455049</v>
+        <v>128454343</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,21 +4879,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586957</v>
+        <v>586829</v>
       </c>
       <c r="R44" t="n">
-        <v>7090160</v>
+        <v>7090210</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4965,32 +4965,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128456473</v>
+        <v>128454373</v>
       </c>
       <c r="B45" t="n">
-        <v>92794</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586959</v>
+        <v>586837</v>
       </c>
       <c r="R45" t="n">
-        <v>7090058</v>
+        <v>7090202</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5062,10 +5062,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128457243</v>
+        <v>128455049</v>
       </c>
       <c r="B46" t="n">
-        <v>78786</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586620</v>
+        <v>586957</v>
       </c>
       <c r="R46" t="n">
-        <v>7090201</v>
+        <v>7090160</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5159,32 +5159,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128456368</v>
+        <v>128454991</v>
       </c>
       <c r="B47" t="n">
-        <v>91469</v>
+        <v>91665</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586986</v>
+        <v>586930</v>
       </c>
       <c r="R47" t="n">
-        <v>7090055</v>
+        <v>7090184</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456539</v>
+        <v>128456368</v>
       </c>
       <c r="B48" t="n">
-        <v>92794</v>
+        <v>91469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5267,21 +5267,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586940</v>
+        <v>586986</v>
       </c>
       <c r="R48" t="n">
-        <v>7090064</v>
+        <v>7090055</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5353,32 +5353,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128454991</v>
+        <v>128456539</v>
       </c>
       <c r="B49" t="n">
-        <v>91665</v>
+        <v>92794</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586930</v>
+        <v>586940</v>
       </c>
       <c r="R49" t="n">
-        <v>7090184</v>
+        <v>7090064</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5450,32 +5450,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128453832</v>
+        <v>128452749</v>
       </c>
       <c r="B50" t="n">
-        <v>92794</v>
+        <v>78786</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586762</v>
+        <v>586640</v>
       </c>
       <c r="R50" t="n">
-        <v>7090294</v>
+        <v>7090343</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5547,32 +5547,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128452749</v>
+        <v>128453832</v>
       </c>
       <c r="B51" t="n">
-        <v>78786</v>
+        <v>92794</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586640</v>
+        <v>586762</v>
       </c>
       <c r="R51" t="n">
-        <v>7090343</v>
+        <v>7090294</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128456430</v>
+        <v>128455401</v>
       </c>
       <c r="B53" t="n">
-        <v>92823</v>
+        <v>78786</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5752,14 +5752,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>353</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5767,10 +5776,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586964</v>
+        <v>587046</v>
       </c>
       <c r="R53" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5829,10 +5838,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128455401</v>
+        <v>128456430</v>
       </c>
       <c r="B54" t="n">
-        <v>78786</v>
+        <v>92823</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5840,23 +5849,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>587046</v>
+        <v>586964</v>
       </c>
       <c r="R54" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5926,32 +5926,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455902</v>
+        <v>128455876</v>
       </c>
       <c r="B55" t="n">
-        <v>92794</v>
+        <v>78786</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5964,7 +5964,7 @@
         <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090163</v>
+        <v>7090165</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128455058</v>
+        <v>128457035</v>
       </c>
       <c r="B57" t="n">
         <v>92794</v>
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586958</v>
+        <v>586687</v>
       </c>
       <c r="R57" t="n">
-        <v>7090158</v>
+        <v>7090150</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128457035</v>
+        <v>128455902</v>
       </c>
       <c r="B58" t="n">
         <v>92794</v>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586687</v>
+        <v>587083</v>
       </c>
       <c r="R58" t="n">
-        <v>7090150</v>
+        <v>7090163</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6314,32 +6314,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455876</v>
+        <v>128455058</v>
       </c>
       <c r="B59" t="n">
-        <v>78786</v>
+        <v>92794</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587083</v>
+        <v>586958</v>
       </c>
       <c r="R59" t="n">
-        <v>7090165</v>
+        <v>7090158</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6411,7 +6411,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128454284</v>
+        <v>128452666</v>
       </c>
       <c r="B60" t="n">
         <v>78877</v>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586798</v>
+        <v>586636</v>
       </c>
       <c r="R60" t="n">
-        <v>7090261</v>
+        <v>7090355</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6508,7 +6508,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128452666</v>
+        <v>128454284</v>
       </c>
       <c r="B61" t="n">
         <v>78877</v>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586636</v>
+        <v>586798</v>
       </c>
       <c r="R61" t="n">
-        <v>7090355</v>
+        <v>7090261</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>128454303</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128452297</v>
+        <v>128456150</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586593</v>
+        <v>587092</v>
       </c>
       <c r="R7" t="n">
-        <v>7090373</v>
+        <v>7090041</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128456150</v>
+        <v>128452297</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>79743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,21 +1396,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587092</v>
+        <v>586593</v>
       </c>
       <c r="R8" t="n">
-        <v>7090041</v>
+        <v>7090373</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128456020</v>
+        <v>128456801</v>
       </c>
       <c r="B9" t="n">
-        <v>92794</v>
+        <v>91669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587087</v>
+        <v>586808</v>
       </c>
       <c r="R9" t="n">
-        <v>7090081</v>
+        <v>7090047</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456801</v>
+        <v>128456020</v>
       </c>
       <c r="B10" t="n">
-        <v>91665</v>
+        <v>92798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586808</v>
+        <v>587087</v>
       </c>
       <c r="R10" t="n">
-        <v>7090047</v>
+        <v>7090081</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1679,7 +1679,7 @@
         <v>128453289</v>
       </c>
       <c r="B11" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128456148</v>
+        <v>128454030</v>
       </c>
       <c r="B12" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587092</v>
+        <v>586773</v>
       </c>
       <c r="R12" t="n">
-        <v>7090041</v>
+        <v>7090298</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128454030</v>
+        <v>128456148</v>
       </c>
       <c r="B13" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586773</v>
+        <v>587092</v>
       </c>
       <c r="R13" t="n">
-        <v>7090298</v>
+        <v>7090041</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1970,7 +1970,7 @@
         <v>128456677</v>
       </c>
       <c r="B14" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>128453887</v>
       </c>
       <c r="B15" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,34 +2161,25 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B16" t="n">
-        <v>92794</v>
+        <v>92827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2196,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R16" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,25 +2249,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B17" t="n">
-        <v>92823</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R17" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2349,7 +2349,7 @@
         <v>128453418</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128452869</v>
       </c>
       <c r="B19" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,32 +2540,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128454471</v>
+        <v>128456660</v>
       </c>
       <c r="B20" t="n">
-        <v>78877</v>
+        <v>80257</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586884</v>
+        <v>586916</v>
       </c>
       <c r="R20" t="n">
-        <v>7090162</v>
+        <v>7090085</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2637,32 +2637,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128456660</v>
+        <v>128454471</v>
       </c>
       <c r="B21" t="n">
-        <v>80253</v>
+        <v>78881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586916</v>
+        <v>586884</v>
       </c>
       <c r="R21" t="n">
-        <v>7090085</v>
+        <v>7090162</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2734,32 +2734,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128454384</v>
+        <v>128453928</v>
       </c>
       <c r="B22" t="n">
-        <v>92794</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586835</v>
+        <v>586768</v>
       </c>
       <c r="R22" t="n">
-        <v>7090189</v>
+        <v>7090309</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2831,32 +2831,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128453928</v>
+        <v>128454384</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>92798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586768</v>
+        <v>586835</v>
       </c>
       <c r="R23" t="n">
-        <v>7090309</v>
+        <v>7090189</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2928,32 +2928,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128452701</v>
+        <v>128455293</v>
       </c>
       <c r="B24" t="n">
-        <v>92794</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586641</v>
+        <v>587050</v>
       </c>
       <c r="R24" t="n">
-        <v>7090355</v>
+        <v>7090143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3028,7 +3028,7 @@
         <v>128456875</v>
       </c>
       <c r="B25" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3122,32 +3122,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128452844</v>
+        <v>128452701</v>
       </c>
       <c r="B26" t="n">
-        <v>80225</v>
+        <v>92798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586675</v>
+        <v>586641</v>
       </c>
       <c r="R26" t="n">
-        <v>7090334</v>
+        <v>7090355</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128455293</v>
+        <v>128452844</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587050</v>
+        <v>586675</v>
       </c>
       <c r="R27" t="n">
-        <v>7090143</v>
+        <v>7090334</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3319,7 +3319,7 @@
         <v>128455272</v>
       </c>
       <c r="B28" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128454846</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128455546</v>
       </c>
       <c r="B30" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,32 +3607,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128456386</v>
+        <v>128454639</v>
       </c>
       <c r="B31" t="n">
-        <v>92806</v>
+        <v>78790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586982</v>
+        <v>586863</v>
       </c>
       <c r="R31" t="n">
-        <v>7090061</v>
+        <v>7090231</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128455740</v>
+        <v>128456612</v>
       </c>
       <c r="B32" t="n">
-        <v>92798</v>
+        <v>79743</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587055</v>
+        <v>586932</v>
       </c>
       <c r="R32" t="n">
-        <v>7090173</v>
+        <v>7090054</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3804,7 +3804,7 @@
         <v>128456454</v>
       </c>
       <c r="B33" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3898,32 +3898,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128456612</v>
+        <v>128456386</v>
       </c>
       <c r="B34" t="n">
-        <v>79739</v>
+        <v>92810</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586932</v>
+        <v>586982</v>
       </c>
       <c r="R34" t="n">
-        <v>7090054</v>
+        <v>7090061</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3995,32 +3995,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128454639</v>
+        <v>128452918</v>
       </c>
       <c r="B35" t="n">
-        <v>78786</v>
+        <v>92798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586863</v>
+        <v>586693</v>
       </c>
       <c r="R35" t="n">
-        <v>7090231</v>
+        <v>7090373</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4092,32 +4092,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128452918</v>
+        <v>128455740</v>
       </c>
       <c r="B36" t="n">
-        <v>92794</v>
+        <v>92802</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586693</v>
+        <v>587055</v>
       </c>
       <c r="R36" t="n">
-        <v>7090373</v>
+        <v>7090173</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4192,7 +4192,7 @@
         <v>128453864</v>
       </c>
       <c r="B37" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128452657</v>
+        <v>128454684</v>
       </c>
       <c r="B38" t="n">
-        <v>78092</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4297,21 +4297,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586636</v>
+        <v>586912</v>
       </c>
       <c r="R38" t="n">
-        <v>7090354</v>
+        <v>7090206</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128454684</v>
+        <v>128454512</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586912</v>
+        <v>586853</v>
       </c>
       <c r="R39" t="n">
-        <v>7090206</v>
+        <v>7090161</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128454512</v>
+        <v>128455537</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586853</v>
+        <v>587026</v>
       </c>
       <c r="R40" t="n">
-        <v>7090161</v>
+        <v>7090169</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128455537</v>
+        <v>128452657</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>78096</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587026</v>
+        <v>586636</v>
       </c>
       <c r="R41" t="n">
-        <v>7090169</v>
+        <v>7090354</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4674,32 +4674,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128456473</v>
+        <v>128457243</v>
       </c>
       <c r="B42" t="n">
-        <v>92794</v>
+        <v>78790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586959</v>
+        <v>586620</v>
       </c>
       <c r="R42" t="n">
-        <v>7090058</v>
+        <v>7090201</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128457243</v>
+        <v>128454373</v>
       </c>
       <c r="B43" t="n">
-        <v>78786</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586620</v>
+        <v>586837</v>
       </c>
       <c r="R43" t="n">
-        <v>7090201</v>
+        <v>7090202</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4871,7 +4871,7 @@
         <v>128454343</v>
       </c>
       <c r="B44" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4965,10 +4965,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128454373</v>
+        <v>128455049</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586837</v>
+        <v>586957</v>
       </c>
       <c r="R45" t="n">
-        <v>7090202</v>
+        <v>7090160</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5062,32 +5062,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128455049</v>
+        <v>128456473</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>92798</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586957</v>
+        <v>586959</v>
       </c>
       <c r="R46" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5159,32 +5159,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128454991</v>
+        <v>128456539</v>
       </c>
       <c r="B47" t="n">
-        <v>91665</v>
+        <v>92798</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586930</v>
+        <v>586940</v>
       </c>
       <c r="R47" t="n">
-        <v>7090184</v>
+        <v>7090064</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5259,7 +5259,7 @@
         <v>128456368</v>
       </c>
       <c r="B48" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,32 +5353,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128456539</v>
+        <v>128454991</v>
       </c>
       <c r="B49" t="n">
-        <v>92794</v>
+        <v>91669</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586940</v>
+        <v>586930</v>
       </c>
       <c r="R49" t="n">
-        <v>7090064</v>
+        <v>7090184</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5450,32 +5450,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128452749</v>
+        <v>128453832</v>
       </c>
       <c r="B50" t="n">
-        <v>78786</v>
+        <v>92798</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586640</v>
+        <v>586762</v>
       </c>
       <c r="R50" t="n">
-        <v>7090343</v>
+        <v>7090294</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5547,32 +5547,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128453832</v>
+        <v>128452749</v>
       </c>
       <c r="B51" t="n">
-        <v>92794</v>
+        <v>78790</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586762</v>
+        <v>586640</v>
       </c>
       <c r="R51" t="n">
-        <v>7090294</v>
+        <v>7090343</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5647,7 +5647,7 @@
         <v>128453795</v>
       </c>
       <c r="B52" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128455401</v>
+        <v>128456430</v>
       </c>
       <c r="B53" t="n">
-        <v>78786</v>
+        <v>92827</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5752,23 +5752,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5776,10 +5767,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>587046</v>
+        <v>586964</v>
       </c>
       <c r="R53" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5838,10 +5829,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128456430</v>
+        <v>128455401</v>
       </c>
       <c r="B54" t="n">
-        <v>92823</v>
+        <v>78790</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5849,14 +5840,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>353</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586964</v>
+        <v>587046</v>
       </c>
       <c r="R54" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5929,7 +5929,7 @@
         <v>128455876</v>
       </c>
       <c r="B55" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6023,10 +6023,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128455941</v>
+        <v>128454284</v>
       </c>
       <c r="B56" t="n">
-        <v>92788</v>
+        <v>78881</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6034,21 +6034,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587080</v>
+        <v>586798</v>
       </c>
       <c r="R56" t="n">
-        <v>7090141</v>
+        <v>7090261</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6120,32 +6120,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128457035</v>
+        <v>128452666</v>
       </c>
       <c r="B57" t="n">
-        <v>92794</v>
+        <v>78881</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586687</v>
+        <v>586636</v>
       </c>
       <c r="R57" t="n">
-        <v>7090150</v>
+        <v>7090355</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6220,7 +6220,7 @@
         <v>128455902</v>
       </c>
       <c r="B58" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6314,32 +6314,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455058</v>
+        <v>128455941</v>
       </c>
       <c r="B59" t="n">
-        <v>92794</v>
+        <v>92792</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586958</v>
+        <v>587080</v>
       </c>
       <c r="R59" t="n">
-        <v>7090158</v>
+        <v>7090141</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6411,32 +6411,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128452666</v>
+        <v>128455058</v>
       </c>
       <c r="B60" t="n">
-        <v>78877</v>
+        <v>92798</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586636</v>
+        <v>586958</v>
       </c>
       <c r="R60" t="n">
-        <v>7090355</v>
+        <v>7090158</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6508,32 +6508,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128454284</v>
+        <v>128457035</v>
       </c>
       <c r="B61" t="n">
-        <v>78877</v>
+        <v>92798</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586798</v>
+        <v>586687</v>
       </c>
       <c r="R61" t="n">
-        <v>7090261</v>
+        <v>7090150</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6605,32 +6605,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B62" t="n">
-        <v>92794</v>
+        <v>78881</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R62" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6702,32 +6702,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B63" t="n">
-        <v>78877</v>
+        <v>92798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R63" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6799,10 +6799,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B64" t="n">
-        <v>78786</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R64" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6896,10 +6896,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B65" t="n">
-        <v>79120</v>
+        <v>78790</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6907,21 +6907,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R65" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -5159,32 +5159,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128456539</v>
+        <v>128454991</v>
       </c>
       <c r="B47" t="n">
-        <v>92798</v>
+        <v>91669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586940</v>
+        <v>586930</v>
       </c>
       <c r="R47" t="n">
-        <v>7090064</v>
+        <v>7090184</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456368</v>
+        <v>128456539</v>
       </c>
       <c r="B48" t="n">
-        <v>91473</v>
+        <v>92798</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5267,21 +5267,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586986</v>
+        <v>586940</v>
       </c>
       <c r="R48" t="n">
-        <v>7090055</v>
+        <v>7090064</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5353,32 +5353,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128454991</v>
+        <v>128456368</v>
       </c>
       <c r="B49" t="n">
-        <v>91669</v>
+        <v>91473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586930</v>
+        <v>586986</v>
       </c>
       <c r="R49" t="n">
-        <v>7090184</v>
+        <v>7090055</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5450,32 +5450,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128453832</v>
+        <v>128452749</v>
       </c>
       <c r="B50" t="n">
-        <v>92798</v>
+        <v>78790</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586762</v>
+        <v>586640</v>
       </c>
       <c r="R50" t="n">
-        <v>7090294</v>
+        <v>7090343</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5547,10 +5547,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128452749</v>
+        <v>128453795</v>
       </c>
       <c r="B51" t="n">
-        <v>78790</v>
+        <v>78881</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586640</v>
+        <v>586761</v>
       </c>
       <c r="R51" t="n">
-        <v>7090343</v>
+        <v>7090287</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5644,32 +5644,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128453795</v>
+        <v>128453832</v>
       </c>
       <c r="B52" t="n">
-        <v>78881</v>
+        <v>92798</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586761</v>
+        <v>586762</v>
       </c>
       <c r="R52" t="n">
-        <v>7090287</v>
+        <v>7090294</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128456430</v>
+        <v>128455401</v>
       </c>
       <c r="B53" t="n">
-        <v>92827</v>
+        <v>78790</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5752,14 +5752,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>353</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5767,10 +5776,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>586964</v>
+        <v>587046</v>
       </c>
       <c r="R53" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5829,10 +5838,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128455401</v>
+        <v>128456430</v>
       </c>
       <c r="B54" t="n">
-        <v>78790</v>
+        <v>92827</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5840,23 +5849,14 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>587046</v>
+        <v>586964</v>
       </c>
       <c r="R54" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6605,32 +6605,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B62" t="n">
-        <v>78881</v>
+        <v>92798</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R62" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6702,32 +6702,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B63" t="n">
-        <v>92798</v>
+        <v>78881</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R63" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>128454303</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>128456150</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128452297</v>
       </c>
       <c r="B8" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,32 +1482,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128456801</v>
+        <v>128453289</v>
       </c>
       <c r="B9" t="n">
-        <v>91669</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586808</v>
+        <v>586738</v>
       </c>
       <c r="R9" t="n">
-        <v>7090047</v>
+        <v>7090296</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456020</v>
+        <v>128456801</v>
       </c>
       <c r="B10" t="n">
-        <v>92798</v>
+        <v>91674</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587087</v>
+        <v>586808</v>
       </c>
       <c r="R10" t="n">
-        <v>7090081</v>
+        <v>7090047</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128453289</v>
+        <v>128456020</v>
       </c>
       <c r="B11" t="n">
-        <v>91528</v>
+        <v>92803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586738</v>
+        <v>587087</v>
       </c>
       <c r="R11" t="n">
-        <v>7090296</v>
+        <v>7090081</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1776,7 +1776,7 @@
         <v>128454030</v>
       </c>
       <c r="B12" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>128456148</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128456677</v>
       </c>
       <c r="B14" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>128453887</v>
       </c>
       <c r="B15" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,25 +2161,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128455756</v>
+        <v>128454707</v>
       </c>
       <c r="B16" t="n">
-        <v>92827</v>
+        <v>92803</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2187,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587055</v>
+        <v>586897</v>
       </c>
       <c r="R16" t="n">
-        <v>7090173</v>
+        <v>7090212</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2249,34 +2258,25 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128454707</v>
+        <v>128455756</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586897</v>
+        <v>587055</v>
       </c>
       <c r="R17" t="n">
-        <v>7090212</v>
+        <v>7090173</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2349,7 +2349,7 @@
         <v>128453418</v>
       </c>
       <c r="B18" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>128452869</v>
       </c>
       <c r="B19" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128456660</v>
+        <v>128454384</v>
       </c>
       <c r="B20" t="n">
-        <v>80257</v>
+        <v>92803</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,21 +2551,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586916</v>
+        <v>586835</v>
       </c>
       <c r="R20" t="n">
-        <v>7090085</v>
+        <v>7090189</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2637,32 +2637,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128454471</v>
+        <v>128456660</v>
       </c>
       <c r="B21" t="n">
-        <v>78881</v>
+        <v>80162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586884</v>
+        <v>586916</v>
       </c>
       <c r="R21" t="n">
-        <v>7090162</v>
+        <v>7090085</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128453928</v>
+        <v>128454471</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,21 +2745,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586768</v>
+        <v>586884</v>
       </c>
       <c r="R22" t="n">
-        <v>7090309</v>
+        <v>7090162</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2831,32 +2831,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128454384</v>
+        <v>128453928</v>
       </c>
       <c r="B23" t="n">
-        <v>92798</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586835</v>
+        <v>586768</v>
       </c>
       <c r="R23" t="n">
-        <v>7090189</v>
+        <v>7090309</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2928,32 +2928,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128455293</v>
+        <v>128452701</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>92803</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587050</v>
+        <v>586641</v>
       </c>
       <c r="R24" t="n">
-        <v>7090143</v>
+        <v>7090355</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128456875</v>
+        <v>128455293</v>
       </c>
       <c r="B25" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3036,21 +3036,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586751</v>
+        <v>587050</v>
       </c>
       <c r="R25" t="n">
-        <v>7090092</v>
+        <v>7090143</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,32 +3122,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128452701</v>
+        <v>128452844</v>
       </c>
       <c r="B26" t="n">
-        <v>92798</v>
+        <v>80134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586641</v>
+        <v>586675</v>
       </c>
       <c r="R26" t="n">
-        <v>7090355</v>
+        <v>7090334</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128452844</v>
+        <v>128456875</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>78786</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586675</v>
+        <v>586751</v>
       </c>
       <c r="R27" t="n">
-        <v>7090334</v>
+        <v>7090092</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3319,7 +3319,7 @@
         <v>128455272</v>
       </c>
       <c r="B28" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128454846</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128455546</v>
       </c>
       <c r="B30" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>128454639</v>
       </c>
       <c r="B31" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>128456612</v>
       </c>
       <c r="B32" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>128456454</v>
       </c>
       <c r="B33" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>128456386</v>
       </c>
       <c r="B34" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>128452918</v>
       </c>
       <c r="B35" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>128455740</v>
       </c>
       <c r="B36" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>128453864</v>
       </c>
       <c r="B37" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>128454684</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>128454512</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128455537</v>
+        <v>128452657</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>78037</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587026</v>
+        <v>586636</v>
       </c>
       <c r="R40" t="n">
-        <v>7090169</v>
+        <v>7090354</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128452657</v>
+        <v>128455537</v>
       </c>
       <c r="B41" t="n">
-        <v>78096</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586636</v>
+        <v>587026</v>
       </c>
       <c r="R41" t="n">
-        <v>7090354</v>
+        <v>7090169</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4674,10 +4674,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128457243</v>
+        <v>128454373</v>
       </c>
       <c r="B42" t="n">
-        <v>78790</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4685,21 +4685,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586620</v>
+        <v>586837</v>
       </c>
       <c r="R42" t="n">
-        <v>7090201</v>
+        <v>7090202</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128454373</v>
+        <v>128454343</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586837</v>
+        <v>586829</v>
       </c>
       <c r="R43" t="n">
-        <v>7090202</v>
+        <v>7090210</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128454343</v>
+        <v>128455049</v>
       </c>
       <c r="B44" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,21 +4879,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586829</v>
+        <v>586957</v>
       </c>
       <c r="R44" t="n">
-        <v>7090210</v>
+        <v>7090160</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4965,32 +4965,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128455049</v>
+        <v>128456473</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>92803</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586957</v>
+        <v>586959</v>
       </c>
       <c r="R45" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5062,32 +5062,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128456473</v>
+        <v>128457243</v>
       </c>
       <c r="B46" t="n">
-        <v>92798</v>
+        <v>78695</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586959</v>
+        <v>586620</v>
       </c>
       <c r="R46" t="n">
-        <v>7090058</v>
+        <v>7090201</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5159,32 +5159,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128454991</v>
+        <v>128456368</v>
       </c>
       <c r="B47" t="n">
-        <v>91669</v>
+        <v>91478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586930</v>
+        <v>586986</v>
       </c>
       <c r="R47" t="n">
-        <v>7090184</v>
+        <v>7090055</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5256,32 +5256,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456539</v>
+        <v>128454991</v>
       </c>
       <c r="B48" t="n">
-        <v>92798</v>
+        <v>91674</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586940</v>
+        <v>586930</v>
       </c>
       <c r="R48" t="n">
-        <v>7090064</v>
+        <v>7090184</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128456368</v>
+        <v>128456539</v>
       </c>
       <c r="B49" t="n">
-        <v>91473</v>
+        <v>92803</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5364,21 +5364,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586986</v>
+        <v>586940</v>
       </c>
       <c r="R49" t="n">
-        <v>7090055</v>
+        <v>7090064</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5450,32 +5450,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128452749</v>
+        <v>128453832</v>
       </c>
       <c r="B50" t="n">
-        <v>78790</v>
+        <v>92803</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586640</v>
+        <v>586762</v>
       </c>
       <c r="R50" t="n">
-        <v>7090343</v>
+        <v>7090294</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5547,10 +5547,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128453795</v>
+        <v>128452749</v>
       </c>
       <c r="B51" t="n">
-        <v>78881</v>
+        <v>78695</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5558,21 +5558,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586761</v>
+        <v>586640</v>
       </c>
       <c r="R51" t="n">
-        <v>7090287</v>
+        <v>7090343</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5644,32 +5644,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128453832</v>
+        <v>128453795</v>
       </c>
       <c r="B52" t="n">
-        <v>92798</v>
+        <v>78786</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586762</v>
+        <v>586761</v>
       </c>
       <c r="R52" t="n">
-        <v>7090294</v>
+        <v>7090287</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128455401</v>
+        <v>128456430</v>
       </c>
       <c r="B53" t="n">
-        <v>78790</v>
+        <v>92832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5752,23 +5752,14 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5776,10 +5767,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>587046</v>
+        <v>586964</v>
       </c>
       <c r="R53" t="n">
-        <v>7090160</v>
+        <v>7090058</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5838,10 +5829,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128456430</v>
+        <v>128455401</v>
       </c>
       <c r="B54" t="n">
-        <v>92827</v>
+        <v>78695</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5849,14 +5840,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>353</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586964</v>
+        <v>587046</v>
       </c>
       <c r="R54" t="n">
-        <v>7090058</v>
+        <v>7090160</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5926,32 +5926,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455876</v>
+        <v>128455902</v>
       </c>
       <c r="B55" t="n">
-        <v>78790</v>
+        <v>92803</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5964,7 +5964,7 @@
         <v>587083</v>
       </c>
       <c r="R55" t="n">
-        <v>7090165</v>
+        <v>7090163</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6023,32 +6023,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128454284</v>
+        <v>128455058</v>
       </c>
       <c r="B56" t="n">
-        <v>78881</v>
+        <v>92803</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>586798</v>
+        <v>586958</v>
       </c>
       <c r="R56" t="n">
-        <v>7090261</v>
+        <v>7090158</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6120,32 +6120,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128452666</v>
+        <v>128457035</v>
       </c>
       <c r="B57" t="n">
-        <v>78881</v>
+        <v>92803</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>586636</v>
+        <v>586687</v>
       </c>
       <c r="R57" t="n">
-        <v>7090355</v>
+        <v>7090150</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6217,32 +6217,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128455902</v>
+        <v>128455941</v>
       </c>
       <c r="B58" t="n">
-        <v>92798</v>
+        <v>92797</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>587083</v>
+        <v>587080</v>
       </c>
       <c r="R58" t="n">
-        <v>7090163</v>
+        <v>7090141</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6314,10 +6314,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128455941</v>
+        <v>128455876</v>
       </c>
       <c r="B59" t="n">
-        <v>92792</v>
+        <v>78695</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>587080</v>
+        <v>587083</v>
       </c>
       <c r="R59" t="n">
-        <v>7090141</v>
+        <v>7090165</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6411,32 +6411,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128455058</v>
+        <v>128454284</v>
       </c>
       <c r="B60" t="n">
-        <v>92798</v>
+        <v>78786</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586958</v>
+        <v>586798</v>
       </c>
       <c r="R60" t="n">
-        <v>7090158</v>
+        <v>7090261</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6508,32 +6508,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128457035</v>
+        <v>128452666</v>
       </c>
       <c r="B61" t="n">
-        <v>92798</v>
+        <v>78786</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586687</v>
+        <v>586636</v>
       </c>
       <c r="R61" t="n">
-        <v>7090150</v>
+        <v>7090355</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6605,32 +6605,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128453037</v>
+        <v>128452593</v>
       </c>
       <c r="B62" t="n">
-        <v>92798</v>
+        <v>78786</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586731</v>
+        <v>586637</v>
       </c>
       <c r="R62" t="n">
-        <v>7090327</v>
+        <v>7090363</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6702,32 +6702,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128452593</v>
+        <v>128453037</v>
       </c>
       <c r="B63" t="n">
-        <v>78881</v>
+        <v>92803</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586637</v>
+        <v>586731</v>
       </c>
       <c r="R63" t="n">
-        <v>7090363</v>
+        <v>7090327</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6799,10 +6799,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128456064</v>
+        <v>128453255</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>78695</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>587101</v>
+        <v>586727</v>
       </c>
       <c r="R64" t="n">
-        <v>7090077</v>
+        <v>7090310</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6896,10 +6896,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128453255</v>
+        <v>128456064</v>
       </c>
       <c r="B65" t="n">
-        <v>78790</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6907,21 +6907,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>586727</v>
+        <v>587101</v>
       </c>
       <c r="R65" t="n">
-        <v>7090310</v>
+        <v>7090077</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75247194</v>
+        <v>128452749</v>
       </c>
       <c r="B2" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587026.0416632686</v>
+        <v>586640</v>
       </c>
       <c r="R2" t="n">
-        <v>7090175.911992747</v>
+        <v>7090343</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,48 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>olikåldrig, brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov, ca 300-årig tall</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75247195</v>
+        <v>128453255</v>
       </c>
       <c r="B3" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586853.1888790153</v>
+        <v>586727</v>
       </c>
       <c r="R3" t="n">
-        <v>7090179.028527888</v>
+        <v>7090310</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,48 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>olikåldrig, brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75247196</v>
+        <v>128454639</v>
       </c>
       <c r="B4" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586819.0942404106</v>
+        <v>586863</v>
       </c>
       <c r="R4" t="n">
-        <v>7090152.992651987</v>
+        <v>7090231</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,48 +950,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>olikåldrig, brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>2 substratenheter # grövre tallhögstubbar</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75247193</v>
+        <v>128457243</v>
       </c>
       <c r="B5" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587265.1420138782</v>
+        <v>586620</v>
       </c>
       <c r="R5" t="n">
-        <v>7089994.182372587</v>
+        <v>7090201</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-07-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,81 +1047,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>olikåldrig, ljus tallskog</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grovbarkig ca 250-årig tall</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128454303</v>
+        <v>75247201</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586789</v>
+        <v>586549</v>
       </c>
       <c r="R6" t="n">
-        <v>7090238</v>
+        <v>7090178</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,48 +1144,65 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sydvänd, brandpåverkad tallskog</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal rest av skorstenshögstubbe</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128456150</v>
+        <v>128456801</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587092</v>
+        <v>586808</v>
       </c>
       <c r="R7" t="n">
-        <v>7090041</v>
+        <v>7090047</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1385,10 +1274,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128452297</v>
+        <v>75247202</v>
       </c>
       <c r="B8" t="n">
-        <v>79648</v>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,37 +1285,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586593</v>
+        <v>586559</v>
       </c>
       <c r="R8" t="n">
-        <v>7090373</v>
+        <v>7090178</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,12 +1339,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,30 +1355,47 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>sydvänd, brandpåverkad tallskog</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128456020</v>
+        <v>128452701</v>
       </c>
       <c r="B9" t="n">
-        <v>92805</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1517,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587087</v>
+        <v>586641</v>
       </c>
       <c r="R9" t="n">
-        <v>7090081</v>
+        <v>7090355</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1579,32 +1485,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128456801</v>
+        <v>128452918</v>
       </c>
       <c r="B10" t="n">
-        <v>91676</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586808</v>
+        <v>586693</v>
       </c>
       <c r="R10" t="n">
-        <v>7090047</v>
+        <v>7090373</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1676,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128453289</v>
+        <v>128453037</v>
       </c>
       <c r="B11" t="n">
-        <v>91535</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,21 +1593,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1617,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586738</v>
+        <v>586731</v>
       </c>
       <c r="R11" t="n">
-        <v>7090296</v>
+        <v>7090327</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1773,14 +1679,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128454030</v>
+        <v>128453418</v>
       </c>
       <c r="B12" t="n">
-        <v>92805</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1808,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586773</v>
+        <v>586731</v>
       </c>
       <c r="R12" t="n">
-        <v>7090298</v>
+        <v>7090285</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1870,14 +1776,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128456148</v>
+        <v>128453832</v>
       </c>
       <c r="B13" t="n">
-        <v>92805</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1905,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587092</v>
+        <v>586762</v>
       </c>
       <c r="R13" t="n">
-        <v>7090041</v>
+        <v>7090294</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1967,10 +1873,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128456677</v>
+        <v>128454030</v>
       </c>
       <c r="B14" t="n">
-        <v>78695</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,21 +1884,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586919</v>
+        <v>586773</v>
       </c>
       <c r="R14" t="n">
-        <v>7090073</v>
+        <v>7090298</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2064,10 +1970,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128453887</v>
+        <v>128454222</v>
       </c>
       <c r="B15" t="n">
-        <v>79648</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,21 +1981,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2005,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586767</v>
+        <v>586793</v>
       </c>
       <c r="R15" t="n">
-        <v>7090284</v>
+        <v>7090239</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2161,14 +2067,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128454707</v>
+        <v>128454330</v>
       </c>
       <c r="B16" t="n">
-        <v>92805</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2196,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586897</v>
+        <v>586818</v>
       </c>
       <c r="R16" t="n">
-        <v>7090212</v>
+        <v>7090210</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128455756</v>
+        <v>128454384</v>
       </c>
       <c r="B17" t="n">
-        <v>92834</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,14 +2175,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2284,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587055</v>
+        <v>586835</v>
       </c>
       <c r="R17" t="n">
-        <v>7090173</v>
+        <v>7090189</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2346,32 +2261,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128452869</v>
+        <v>128456759</v>
       </c>
       <c r="B18" t="n">
-        <v>80163</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2381,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586682</v>
+        <v>586812</v>
       </c>
       <c r="R18" t="n">
-        <v>7090334</v>
+        <v>7090041</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2443,14 +2358,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128453418</v>
+        <v>128457035</v>
       </c>
       <c r="B19" t="n">
-        <v>92805</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2478,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586731</v>
+        <v>586687</v>
       </c>
       <c r="R19" t="n">
-        <v>7090285</v>
+        <v>7090150</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2540,32 +2455,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128453928</v>
+        <v>128453864</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>93201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2490,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586768</v>
+        <v>586776</v>
       </c>
       <c r="R20" t="n">
-        <v>7090309</v>
+        <v>7090285</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2637,32 +2552,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128454384</v>
+        <v>128453289</v>
       </c>
       <c r="B21" t="n">
-        <v>92805</v>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2587,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586835</v>
+        <v>586738</v>
       </c>
       <c r="R21" t="n">
-        <v>7090189</v>
+        <v>7090296</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2734,32 +2649,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128456660</v>
+        <v>128453928</v>
       </c>
       <c r="B22" t="n">
-        <v>80162</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2769,10 +2684,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586916</v>
+        <v>586768</v>
       </c>
       <c r="R22" t="n">
-        <v>7090085</v>
+        <v>7090309</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2831,32 +2746,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128454471</v>
+        <v>128454303</v>
       </c>
       <c r="B23" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2781,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586884</v>
+        <v>586789</v>
       </c>
       <c r="R23" t="n">
-        <v>7090162</v>
+        <v>7090238</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2928,32 +2843,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128452701</v>
+        <v>128454373</v>
       </c>
       <c r="B24" t="n">
-        <v>92805</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2878,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586641</v>
+        <v>586837</v>
       </c>
       <c r="R24" t="n">
-        <v>7090355</v>
+        <v>7090202</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3025,14 +2940,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128455293</v>
+        <v>128454512</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3060,10 +2975,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587050</v>
+        <v>586853</v>
       </c>
       <c r="R25" t="n">
-        <v>7090143</v>
+        <v>7090161</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,10 +3037,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128452844</v>
+        <v>128452593</v>
       </c>
       <c r="B26" t="n">
-        <v>80134</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,21 +3048,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3157,10 +3072,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586675</v>
+        <v>586637</v>
       </c>
       <c r="R26" t="n">
-        <v>7090334</v>
+        <v>7090363</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3219,10 +3134,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128456875</v>
+        <v>128452666</v>
       </c>
       <c r="B27" t="n">
-        <v>78786</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,10 +3169,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586751</v>
+        <v>586636</v>
       </c>
       <c r="R27" t="n">
-        <v>7090092</v>
+        <v>7090355</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3231,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128455272</v>
+        <v>128453795</v>
       </c>
       <c r="B28" t="n">
-        <v>92805</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587051</v>
+        <v>586761</v>
       </c>
       <c r="R28" t="n">
-        <v>7090142</v>
+        <v>7090287</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3413,10 +3328,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128454846</v>
+        <v>128454284</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3424,21 +3339,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3363,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586924</v>
+        <v>586798</v>
       </c>
       <c r="R29" t="n">
-        <v>7090205</v>
+        <v>7090261</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3510,10 +3425,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128455546</v>
+        <v>128454343</v>
       </c>
       <c r="B30" t="n">
-        <v>78786</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3545,10 +3460,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587028</v>
+        <v>586829</v>
       </c>
       <c r="R30" t="n">
-        <v>7090170</v>
+        <v>7090210</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3607,10 +3522,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128454639</v>
+        <v>128456763</v>
       </c>
       <c r="B31" t="n">
-        <v>78695</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,21 +3533,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586863</v>
+        <v>586812</v>
       </c>
       <c r="R31" t="n">
-        <v>7090231</v>
+        <v>7090041</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3704,32 +3619,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128452918</v>
+        <v>128456875</v>
       </c>
       <c r="B32" t="n">
-        <v>92805</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586693</v>
+        <v>586751</v>
       </c>
       <c r="R32" t="n">
-        <v>7090373</v>
+        <v>7090092</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3801,32 +3716,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128456386</v>
+        <v>128452297</v>
       </c>
       <c r="B33" t="n">
-        <v>92817</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586982</v>
+        <v>586593</v>
       </c>
       <c r="R33" t="n">
-        <v>7090061</v>
+        <v>7090373</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3898,32 +3813,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128455740</v>
+        <v>128453887</v>
       </c>
       <c r="B34" t="n">
-        <v>92809</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587055</v>
+        <v>586767</v>
       </c>
       <c r="R34" t="n">
-        <v>7090173</v>
+        <v>7090284</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3995,10 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128456612</v>
+        <v>128452844</v>
       </c>
       <c r="B35" t="n">
-        <v>79648</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +3921,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586932</v>
+        <v>586675</v>
       </c>
       <c r="R35" t="n">
-        <v>7090054</v>
+        <v>7090334</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4092,32 +4007,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128456454</v>
+        <v>128452869</v>
       </c>
       <c r="B36" t="n">
-        <v>79648</v>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4127,10 +4042,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586965</v>
+        <v>586682</v>
       </c>
       <c r="R36" t="n">
-        <v>7090059</v>
+        <v>7090334</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4189,10 +4104,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128454684</v>
+        <v>75247195</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>78334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4200,37 +4115,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586912</v>
+        <v>586853</v>
       </c>
       <c r="R37" t="n">
-        <v>7090206</v>
+        <v>7090179</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4254,12 +4169,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4270,26 +4185,43 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>olikåldrig, brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AN37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov tallhögstubbe</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128454512</v>
+        <v>128452657</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>78334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4297,21 +4229,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4321,10 +4253,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586853</v>
+        <v>586636</v>
       </c>
       <c r="R38" t="n">
-        <v>7090161</v>
+        <v>7090354</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,10 +4315,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128455537</v>
+        <v>75247196</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4394,37 +4326,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+          <t>Nybäcksberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587026</v>
+        <v>586819</v>
       </c>
       <c r="R39" t="n">
-        <v>7090169</v>
+        <v>7090153</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4448,12 +4380,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2018-07-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4464,26 +4396,43 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>olikåldrig, brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AN39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>2 substratenheter # grövre tallhögstubbar</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128452657</v>
+        <v>128455401</v>
       </c>
       <c r="B40" t="n">
-        <v>78037</v>
+        <v>78993</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4440,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4464,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586636</v>
+        <v>587046</v>
       </c>
       <c r="R40" t="n">
-        <v>7090354</v>
+        <v>7090160</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,32 +4526,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128453864</v>
+        <v>128455876</v>
       </c>
       <c r="B41" t="n">
-        <v>92809</v>
+        <v>78993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4561,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586776</v>
+        <v>587083</v>
       </c>
       <c r="R41" t="n">
-        <v>7090285</v>
+        <v>7090165</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4674,10 +4623,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128457243</v>
+        <v>128456677</v>
       </c>
       <c r="B42" t="n">
-        <v>78695</v>
+        <v>78993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4709,10 +4658,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586620</v>
+        <v>586919</v>
       </c>
       <c r="R42" t="n">
-        <v>7090201</v>
+        <v>7090073</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,32 +4720,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128456473</v>
+        <v>128454991</v>
       </c>
       <c r="B43" t="n">
-        <v>92805</v>
+        <v>92083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4806,10 +4755,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586959</v>
+        <v>586930</v>
       </c>
       <c r="R43" t="n">
-        <v>7090058</v>
+        <v>7090184</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4868,10 +4817,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128454373</v>
+        <v>128455941</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>93191</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,21 +4828,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4903,10 +4852,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586837</v>
+        <v>587080</v>
       </c>
       <c r="R44" t="n">
-        <v>7090202</v>
+        <v>7090141</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4965,10 +4914,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128454343</v>
+        <v>128454707</v>
       </c>
       <c r="B45" t="n">
-        <v>78786</v>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4976,21 +4925,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5000,10 +4949,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586829</v>
+        <v>586897</v>
       </c>
       <c r="R45" t="n">
-        <v>7090210</v>
+        <v>7090212</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5062,10 +5011,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128455049</v>
+        <v>128455058</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5073,21 +5022,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5097,10 +5046,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586957</v>
+        <v>586958</v>
       </c>
       <c r="R46" t="n">
-        <v>7090160</v>
+        <v>7090158</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5159,32 +5108,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128454991</v>
+        <v>128455272</v>
       </c>
       <c r="B47" t="n">
-        <v>91676</v>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5194,10 +5143,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586930</v>
+        <v>587051</v>
       </c>
       <c r="R47" t="n">
-        <v>7090184</v>
+        <v>7090142</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5256,14 +5205,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128456539</v>
+        <v>128455902</v>
       </c>
       <c r="B48" t="n">
-        <v>92805</v>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5291,10 +5240,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586940</v>
+        <v>587083</v>
       </c>
       <c r="R48" t="n">
-        <v>7090064</v>
+        <v>7090163</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5353,32 +5302,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128456368</v>
+        <v>128456020</v>
       </c>
       <c r="B49" t="n">
-        <v>91480</v>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5388,10 +5337,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586986</v>
+        <v>587087</v>
       </c>
       <c r="R49" t="n">
-        <v>7090055</v>
+        <v>7090081</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5450,10 +5399,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128452749</v>
+        <v>128456148</v>
       </c>
       <c r="B50" t="n">
-        <v>78695</v>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,21 +5410,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5485,10 +5434,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586640</v>
+        <v>587092</v>
       </c>
       <c r="R50" t="n">
-        <v>7090343</v>
+        <v>7090041</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5547,14 +5496,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128453832</v>
+        <v>128456473</v>
       </c>
       <c r="B51" t="n">
-        <v>92805</v>
+        <v>93197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5582,10 +5531,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586762</v>
+        <v>586959</v>
       </c>
       <c r="R51" t="n">
-        <v>7090294</v>
+        <v>7090058</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5644,10 +5593,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128453795</v>
+        <v>128456539</v>
       </c>
       <c r="B52" t="n">
-        <v>78786</v>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5655,21 +5604,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5679,10 +5628,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586761</v>
+        <v>586940</v>
       </c>
       <c r="R52" t="n">
-        <v>7090287</v>
+        <v>7090064</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5741,32 +5690,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128455401</v>
+        <v>128455740</v>
       </c>
       <c r="B53" t="n">
-        <v>78695</v>
+        <v>93201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5776,10 +5725,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>587046</v>
+        <v>587055</v>
       </c>
       <c r="R53" t="n">
-        <v>7090160</v>
+        <v>7090173</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5838,10 +5787,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128456430</v>
+        <v>128456386</v>
       </c>
       <c r="B54" t="n">
-        <v>92834</v>
+        <v>93209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5849,14 +5798,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>4366</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -5864,10 +5822,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>586964</v>
+        <v>586982</v>
       </c>
       <c r="R54" t="n">
-        <v>7090058</v>
+        <v>7090061</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5926,32 +5884,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128455876</v>
+        <v>128456368</v>
       </c>
       <c r="B55" t="n">
-        <v>78695</v>
+        <v>91872</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5961,10 +5919,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>587083</v>
+        <v>586986</v>
       </c>
       <c r="R55" t="n">
-        <v>7090165</v>
+        <v>7090055</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6023,32 +5981,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128455902</v>
+        <v>128454684</v>
       </c>
       <c r="B56" t="n">
-        <v>92805</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6058,10 +6016,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>587083</v>
+        <v>586912</v>
       </c>
       <c r="R56" t="n">
-        <v>7090163</v>
+        <v>7090206</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6120,32 +6078,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128455941</v>
+        <v>128454846</v>
       </c>
       <c r="B57" t="n">
-        <v>92799</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6155,10 +6113,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>587080</v>
+        <v>586924</v>
       </c>
       <c r="R57" t="n">
-        <v>7090141</v>
+        <v>7090205</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6217,32 +6175,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128455058</v>
+        <v>128455049</v>
       </c>
       <c r="B58" t="n">
-        <v>92805</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6252,10 +6210,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>586958</v>
+        <v>586957</v>
       </c>
       <c r="R58" t="n">
-        <v>7090158</v>
+        <v>7090160</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6314,32 +6272,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128457035</v>
+        <v>128455293</v>
       </c>
       <c r="B59" t="n">
-        <v>92805</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6349,10 +6307,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>586687</v>
+        <v>587050</v>
       </c>
       <c r="R59" t="n">
-        <v>7090150</v>
+        <v>7090143</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6411,32 +6369,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128454284</v>
+        <v>128455537</v>
       </c>
       <c r="B60" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6446,10 +6404,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>586798</v>
+        <v>587026</v>
       </c>
       <c r="R60" t="n">
-        <v>7090261</v>
+        <v>7090169</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6508,32 +6466,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128452666</v>
+        <v>128456064</v>
       </c>
       <c r="B61" t="n">
-        <v>78786</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6543,10 +6501,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>586636</v>
+        <v>587101</v>
       </c>
       <c r="R61" t="n">
-        <v>7090355</v>
+        <v>7090077</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6605,32 +6563,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128453037</v>
+        <v>128454471</v>
       </c>
       <c r="B62" t="n">
-        <v>92805</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6640,10 +6598,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>586731</v>
+        <v>586884</v>
       </c>
       <c r="R62" t="n">
-        <v>7090327</v>
+        <v>7090162</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6702,10 +6660,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128452593</v>
+        <v>128455546</v>
       </c>
       <c r="B63" t="n">
-        <v>78786</v>
+        <v>79084</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6737,10 +6695,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>586637</v>
+        <v>587028</v>
       </c>
       <c r="R63" t="n">
-        <v>7090363</v>
+        <v>7090170</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6799,10 +6757,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128453255</v>
+        <v>128456150</v>
       </c>
       <c r="B64" t="n">
-        <v>78695</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6810,21 +6768,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6834,10 +6792,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>586727</v>
+        <v>587092</v>
       </c>
       <c r="R64" t="n">
-        <v>7090310</v>
+        <v>7090041</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6896,10 +6854,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128456064</v>
+        <v>128456454</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6907,21 +6865,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6931,10 +6889,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>587101</v>
+        <v>586965</v>
       </c>
       <c r="R65" t="n">
-        <v>7090077</v>
+        <v>7090059</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -6990,6 +6948,428 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128456612</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>586932</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7090054</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128456660</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>586916</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7090085</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>75247193</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>587265</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7089994</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>olikåldrig, ljus tallskog</t>
+        </is>
+      </c>
+      <c r="AN68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grovbarkig ca 250-årig tall</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>75247194</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Nybäcksberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>587026</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7090176</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2018-07-28</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>olikåldrig, brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AN69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov, ca 300-årig tall</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38270-2025 artfynd.xlsx
+++ b/artfynd/A 38270-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452749</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128453255</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454639</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455401</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455876</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456677</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457243</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247201</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454991</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1659,6 +1709,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456801</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,6 +1828,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247202</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1870,6 +1930,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455941</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1967,6 +2032,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452701</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2064,6 +2134,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452918</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2161,6 +2236,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128453037</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128453418</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128453832</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2452,6 +2542,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454030</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2549,6 +2644,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454222</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2646,6 +2746,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454330</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2743,6 +2848,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454384</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2840,6 +2950,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454707</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2937,6 +3052,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455058</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3034,6 +3154,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455272</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3131,6 +3256,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455902</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3228,6 +3358,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456020</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3325,6 +3460,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456148</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3422,6 +3562,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456473</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3519,6 +3664,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456539</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3616,6 +3766,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456759</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3713,6 +3868,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457035</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3810,6 +3970,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128453864</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3907,6 +4072,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455740</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4004,6 +4174,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456386</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4101,6 +4276,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128453289</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4198,6 +4378,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456368</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4295,6 +4480,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128453928</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4392,6 +4582,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454303</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4489,6 +4684,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454373</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4586,6 +4786,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454512</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4683,6 +4888,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454684</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4780,6 +4990,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454846</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4877,6 +5092,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455049</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4974,6 +5194,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455293</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5071,6 +5296,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455537</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5168,6 +5398,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456064</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5265,6 +5500,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452593</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5362,6 +5602,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452666</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5459,6 +5704,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128453795</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5556,6 +5806,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454284</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5653,6 +5908,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454343</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5750,6 +6010,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128454471</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5847,6 +6112,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128455546</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5944,6 +6214,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456150</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6041,6 +6316,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456763</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6138,6 +6418,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456875</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6235,6 +6520,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452297</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6332,6 +6622,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128453887</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6429,6 +6724,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456454</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6526,6 +6826,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456612</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6623,6 +6928,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452844</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6720,6 +7030,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128456660</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6817,6 +7132,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452869</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6931,6 +7251,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247195</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7028,6 +7353,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452657</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7142,6 +7472,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247193</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7256,6 +7591,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247194</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7370,8 +7710,83 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247196</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>